--- a/Emisiones/3.0 HV-HOJAS DE DATOS/P2437-HV-DTS-003 seguridad.xlsx
+++ b/Emisiones/3.0 HV-HOJAS DE DATOS/P2437-HV-DTS-003 seguridad.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1f2e90018362cd82/Escritorio/Ordenar/HVAC/Calculos/Emisiones/3.0 HV-HOJAS DE DATOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="8_{A5C321F7-E801-47C7-A144-C5EBFADE04D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3AA7890-F0B5-4293-A05B-ACF87A08DE5F}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="8_{A5C321F7-E801-47C7-A144-C5EBFADE04D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FB77E99-2EAF-453D-A644-2112B24A61BB}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="ESPECIFICACIÓN" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">ESPECIFICACIÓN!$A$8:$O$62</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">ESPECIFICACIÓN!$A$8:$O$64</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">PORTADA!$A$1:$BZ$66</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">ESPECIFICACIÓN!$1:$7</definedName>
   </definedNames>
@@ -302,9 +302,6 @@
     <t>3.1. La malla domina la pérdida del conjunto; el dimensionamiento por área neta combinada y la ΔP calculada por cierre de orificio (11 Pa) deben verificarse contra el área efectiva (Ak) del fabricante seleccionado (por confirmar con proveedor).</t>
   </si>
   <si>
-    <t>4. Candidatos comerciales</t>
-  </si>
-  <si>
     <t>Tabla 3. Candidatos (consulta 2026-07-23).</t>
   </si>
   <si>
@@ -401,9 +398,6 @@
     <t>5. Instalación</t>
   </si>
   <si>
-    <t>5.1. Montaje a ras de muro exterior con marco perimetral sellado con silicona RTV neutra (compatible con hipoclorito; Chemical Resistance of RTV Silicone Sealants (PDF) (https://irp.cdn-website.com/63168859/files/uploaded/Chemical%20Resistance%20of%20RTV%20Silicone%20Sealants%20Chart.pdf), consulta 2026-07-23) y ferretería inox 316 (A4).</t>
-  </si>
-  <si>
     <t>5.2. Las bocas exteriores se orientan preferentemente a sotavento respecto de las fuentes de cloro de la planta.</t>
   </si>
   <si>
@@ -417,6 +411,33 @@
   </si>
   <si>
     <t>353×336 mm (área facial 0.1187 m²) o similar</t>
+  </si>
+  <si>
+    <r>
+      <t>5.1. Montaje a ras de muro exterior con marco perimetral sellado con silicona RTV neutra (compatible con hipoclorito; Chemical Resistance of RTV Silicone Sealants (PDF) (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="28"/>
+        <color theme="3"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>https://irp.cdn-website.com/63168859/files/uploaded/Chemical%20Resistance%20of%20RTV%20Silicone%20Sealants%20Chart.pdf</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="28"/>
+        <color rgb="FF404040"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>), consulta 2026-07-23) y ferretería inox 316 (A4).</t>
+    </r>
+  </si>
+  <si>
+    <t>4. Proveedores de referencia</t>
   </si>
 </sst>
 </file>
@@ -428,7 +449,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.00000000000000"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -533,18 +554,6 @@
       <name val="Times New Roman"/>
     </font>
     <font>
-      <sz val="26"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="26"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="22"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -583,6 +592,27 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="28"/>
+      <color theme="3"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="28"/>
+      <color rgb="FF404040"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="28"/>
+      <color rgb="FF375623"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="6">
@@ -779,7 +809,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -819,23 +849,71 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
       <protection hidden="1"/>
@@ -849,7 +927,29 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
@@ -857,61 +957,17 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -922,66 +978,46 @@
     <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1200,6 +1236,10 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1519,90 +1559,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:82" s="1" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="58"/>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="59"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="44"/>
-      <c r="P1" s="18"/>
-      <c r="Q1" s="18"/>
-      <c r="R1" s="18"/>
-      <c r="S1" s="18"/>
-      <c r="T1" s="18"/>
-      <c r="U1" s="18"/>
-      <c r="V1" s="18"/>
-      <c r="W1" s="18"/>
-      <c r="X1" s="18"/>
-      <c r="Y1" s="19"/>
-      <c r="Z1" s="50" t="s">
+      <c r="A1" s="73"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="74"/>
+      <c r="I1" s="74"/>
+      <c r="J1" s="74"/>
+      <c r="K1" s="74"/>
+      <c r="L1" s="74"/>
+      <c r="M1" s="75"/>
+      <c r="N1" s="88"/>
+      <c r="O1" s="74"/>
+      <c r="P1" s="47"/>
+      <c r="Q1" s="47"/>
+      <c r="R1" s="47"/>
+      <c r="S1" s="47"/>
+      <c r="T1" s="47"/>
+      <c r="U1" s="47"/>
+      <c r="V1" s="47"/>
+      <c r="W1" s="47"/>
+      <c r="X1" s="47"/>
+      <c r="Y1" s="48"/>
+      <c r="Z1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="AA1" s="18"/>
-      <c r="AB1" s="18"/>
-      <c r="AC1" s="18"/>
-      <c r="AD1" s="18"/>
-      <c r="AE1" s="18"/>
-      <c r="AF1" s="18"/>
-      <c r="AG1" s="18"/>
-      <c r="AH1" s="18"/>
-      <c r="AI1" s="18"/>
-      <c r="AJ1" s="18"/>
-      <c r="AK1" s="18"/>
-      <c r="AL1" s="18"/>
-      <c r="AM1" s="18"/>
-      <c r="AN1" s="18"/>
-      <c r="AO1" s="18"/>
-      <c r="AP1" s="18"/>
-      <c r="AQ1" s="18"/>
-      <c r="AR1" s="18"/>
-      <c r="AS1" s="18"/>
-      <c r="AT1" s="18"/>
-      <c r="AU1" s="18"/>
-      <c r="AV1" s="18"/>
-      <c r="AW1" s="18"/>
-      <c r="AX1" s="18"/>
-      <c r="AY1" s="18"/>
-      <c r="AZ1" s="18"/>
-      <c r="BA1" s="18"/>
-      <c r="BB1" s="19"/>
-      <c r="BC1" s="36" t="s">
+      <c r="AA1" s="47"/>
+      <c r="AB1" s="47"/>
+      <c r="AC1" s="47"/>
+      <c r="AD1" s="47"/>
+      <c r="AE1" s="47"/>
+      <c r="AF1" s="47"/>
+      <c r="AG1" s="47"/>
+      <c r="AH1" s="47"/>
+      <c r="AI1" s="47"/>
+      <c r="AJ1" s="47"/>
+      <c r="AK1" s="47"/>
+      <c r="AL1" s="47"/>
+      <c r="AM1" s="47"/>
+      <c r="AN1" s="47"/>
+      <c r="AO1" s="47"/>
+      <c r="AP1" s="47"/>
+      <c r="AQ1" s="47"/>
+      <c r="AR1" s="47"/>
+      <c r="AS1" s="47"/>
+      <c r="AT1" s="47"/>
+      <c r="AU1" s="47"/>
+      <c r="AV1" s="47"/>
+      <c r="AW1" s="47"/>
+      <c r="AX1" s="47"/>
+      <c r="AY1" s="47"/>
+      <c r="AZ1" s="47"/>
+      <c r="BA1" s="47"/>
+      <c r="BB1" s="48"/>
+      <c r="BC1" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="BD1" s="37"/>
-      <c r="BE1" s="37"/>
-      <c r="BF1" s="37"/>
-      <c r="BG1" s="37"/>
-      <c r="BH1" s="37"/>
-      <c r="BI1" s="37"/>
-      <c r="BJ1" s="37"/>
-      <c r="BK1" s="37"/>
-      <c r="BL1" s="37"/>
-      <c r="BM1" s="37"/>
-      <c r="BN1" s="38"/>
-      <c r="BO1" s="28" t="s">
+      <c r="BD1" s="66"/>
+      <c r="BE1" s="66"/>
+      <c r="BF1" s="66"/>
+      <c r="BG1" s="66"/>
+      <c r="BH1" s="66"/>
+      <c r="BI1" s="66"/>
+      <c r="BJ1" s="66"/>
+      <c r="BK1" s="66"/>
+      <c r="BL1" s="66"/>
+      <c r="BM1" s="66"/>
+      <c r="BN1" s="67"/>
+      <c r="BO1" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="BP1" s="29"/>
-      <c r="BQ1" s="29"/>
-      <c r="BR1" s="29"/>
-      <c r="BS1" s="29"/>
-      <c r="BT1" s="29"/>
-      <c r="BU1" s="29"/>
-      <c r="BV1" s="29"/>
-      <c r="BW1" s="29"/>
-      <c r="BX1" s="29"/>
-      <c r="BY1" s="29"/>
-      <c r="BZ1" s="30"/>
+      <c r="BP1" s="53"/>
+      <c r="BQ1" s="53"/>
+      <c r="BR1" s="53"/>
+      <c r="BS1" s="53"/>
+      <c r="BT1" s="53"/>
+      <c r="BU1" s="53"/>
+      <c r="BV1" s="53"/>
+      <c r="BW1" s="53"/>
+      <c r="BX1" s="53"/>
+      <c r="BY1" s="53"/>
+      <c r="BZ1" s="54"/>
       <c r="CB1" s="11" t="s">
         <v>3</v>
       </c>
@@ -1611,88 +1651,88 @@
       </c>
     </row>
     <row r="2" spans="1:82" s="1" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="33"/>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="41"/>
-      <c r="M2" s="60"/>
-      <c r="N2" s="33"/>
-      <c r="O2" s="41"/>
-      <c r="P2" s="45"/>
-      <c r="Q2" s="45"/>
-      <c r="R2" s="45"/>
-      <c r="S2" s="45"/>
-      <c r="T2" s="45"/>
-      <c r="U2" s="45"/>
-      <c r="V2" s="45"/>
-      <c r="W2" s="45"/>
-      <c r="X2" s="45"/>
-      <c r="Y2" s="23"/>
-      <c r="Z2" s="24"/>
-      <c r="AA2" s="25"/>
-      <c r="AB2" s="25"/>
-      <c r="AC2" s="25"/>
-      <c r="AD2" s="25"/>
-      <c r="AE2" s="25"/>
-      <c r="AF2" s="25"/>
-      <c r="AG2" s="25"/>
-      <c r="AH2" s="25"/>
-      <c r="AI2" s="25"/>
-      <c r="AJ2" s="25"/>
-      <c r="AK2" s="25"/>
-      <c r="AL2" s="25"/>
-      <c r="AM2" s="25"/>
-      <c r="AN2" s="25"/>
-      <c r="AO2" s="25"/>
-      <c r="AP2" s="25"/>
-      <c r="AQ2" s="25"/>
-      <c r="AR2" s="25"/>
-      <c r="AS2" s="25"/>
-      <c r="AT2" s="25"/>
-      <c r="AU2" s="25"/>
-      <c r="AV2" s="25"/>
-      <c r="AW2" s="25"/>
-      <c r="AX2" s="25"/>
-      <c r="AY2" s="25"/>
-      <c r="AZ2" s="25"/>
-      <c r="BA2" s="25"/>
-      <c r="BB2" s="26"/>
-      <c r="BC2" s="36" t="s">
+      <c r="A2" s="69"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
+      <c r="K2" s="76"/>
+      <c r="L2" s="76"/>
+      <c r="M2" s="77"/>
+      <c r="N2" s="69"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="89"/>
+      <c r="R2" s="89"/>
+      <c r="S2" s="89"/>
+      <c r="T2" s="89"/>
+      <c r="U2" s="89"/>
+      <c r="V2" s="89"/>
+      <c r="W2" s="89"/>
+      <c r="X2" s="89"/>
+      <c r="Y2" s="59"/>
+      <c r="Z2" s="49"/>
+      <c r="AA2" s="50"/>
+      <c r="AB2" s="50"/>
+      <c r="AC2" s="50"/>
+      <c r="AD2" s="50"/>
+      <c r="AE2" s="50"/>
+      <c r="AF2" s="50"/>
+      <c r="AG2" s="50"/>
+      <c r="AH2" s="50"/>
+      <c r="AI2" s="50"/>
+      <c r="AJ2" s="50"/>
+      <c r="AK2" s="50"/>
+      <c r="AL2" s="50"/>
+      <c r="AM2" s="50"/>
+      <c r="AN2" s="50"/>
+      <c r="AO2" s="50"/>
+      <c r="AP2" s="50"/>
+      <c r="AQ2" s="50"/>
+      <c r="AR2" s="50"/>
+      <c r="AS2" s="50"/>
+      <c r="AT2" s="50"/>
+      <c r="AU2" s="50"/>
+      <c r="AV2" s="50"/>
+      <c r="AW2" s="50"/>
+      <c r="AX2" s="50"/>
+      <c r="AY2" s="50"/>
+      <c r="AZ2" s="50"/>
+      <c r="BA2" s="50"/>
+      <c r="BB2" s="51"/>
+      <c r="BC2" s="65" t="s">
         <v>5</v>
       </c>
-      <c r="BD2" s="37"/>
-      <c r="BE2" s="37"/>
-      <c r="BF2" s="37"/>
-      <c r="BG2" s="37"/>
-      <c r="BH2" s="37"/>
-      <c r="BI2" s="37"/>
-      <c r="BJ2" s="37"/>
-      <c r="BK2" s="37"/>
-      <c r="BL2" s="37"/>
-      <c r="BM2" s="37"/>
-      <c r="BN2" s="38"/>
-      <c r="BO2" s="28" t="s">
+      <c r="BD2" s="66"/>
+      <c r="BE2" s="66"/>
+      <c r="BF2" s="66"/>
+      <c r="BG2" s="66"/>
+      <c r="BH2" s="66"/>
+      <c r="BI2" s="66"/>
+      <c r="BJ2" s="66"/>
+      <c r="BK2" s="66"/>
+      <c r="BL2" s="66"/>
+      <c r="BM2" s="66"/>
+      <c r="BN2" s="67"/>
+      <c r="BO2" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="BP2" s="29"/>
-      <c r="BQ2" s="29"/>
-      <c r="BR2" s="29"/>
-      <c r="BS2" s="29"/>
-      <c r="BT2" s="29"/>
-      <c r="BU2" s="29"/>
-      <c r="BV2" s="29"/>
-      <c r="BW2" s="29"/>
-      <c r="BX2" s="29"/>
-      <c r="BY2" s="29"/>
-      <c r="BZ2" s="30"/>
+      <c r="BP2" s="53"/>
+      <c r="BQ2" s="53"/>
+      <c r="BR2" s="53"/>
+      <c r="BS2" s="53"/>
+      <c r="BT2" s="53"/>
+      <c r="BU2" s="53"/>
+      <c r="BV2" s="53"/>
+      <c r="BW2" s="53"/>
+      <c r="BX2" s="53"/>
+      <c r="BY2" s="53"/>
+      <c r="BZ2" s="54"/>
       <c r="CB2" s="11" t="s">
         <v>7</v>
       </c>
@@ -1701,348 +1741,348 @@
       </c>
     </row>
     <row r="3" spans="1:82" s="1" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="33"/>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="60"/>
-      <c r="N3" s="33"/>
-      <c r="O3" s="41"/>
-      <c r="P3" s="45"/>
-      <c r="Q3" s="45"/>
-      <c r="R3" s="45"/>
-      <c r="S3" s="45"/>
-      <c r="T3" s="45"/>
-      <c r="U3" s="45"/>
-      <c r="V3" s="45"/>
-      <c r="W3" s="45"/>
-      <c r="X3" s="45"/>
-      <c r="Y3" s="23"/>
-      <c r="Z3" s="50" t="s">
+      <c r="A3" s="69"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="76"/>
+      <c r="K3" s="76"/>
+      <c r="L3" s="76"/>
+      <c r="M3" s="77"/>
+      <c r="N3" s="69"/>
+      <c r="O3" s="76"/>
+      <c r="P3" s="89"/>
+      <c r="Q3" s="89"/>
+      <c r="R3" s="89"/>
+      <c r="S3" s="89"/>
+      <c r="T3" s="89"/>
+      <c r="U3" s="89"/>
+      <c r="V3" s="89"/>
+      <c r="W3" s="89"/>
+      <c r="X3" s="89"/>
+      <c r="Y3" s="59"/>
+      <c r="Z3" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="AA3" s="18"/>
-      <c r="AB3" s="18"/>
-      <c r="AC3" s="18"/>
-      <c r="AD3" s="18"/>
-      <c r="AE3" s="18"/>
-      <c r="AF3" s="18"/>
-      <c r="AG3" s="18"/>
-      <c r="AH3" s="18"/>
-      <c r="AI3" s="18"/>
-      <c r="AJ3" s="18"/>
-      <c r="AK3" s="18"/>
-      <c r="AL3" s="18"/>
-      <c r="AM3" s="18"/>
-      <c r="AN3" s="18"/>
-      <c r="AO3" s="18"/>
-      <c r="AP3" s="18"/>
-      <c r="AQ3" s="18"/>
-      <c r="AR3" s="18"/>
-      <c r="AS3" s="18"/>
-      <c r="AT3" s="18"/>
-      <c r="AU3" s="18"/>
-      <c r="AV3" s="18"/>
-      <c r="AW3" s="18"/>
-      <c r="AX3" s="18"/>
-      <c r="AY3" s="18"/>
-      <c r="AZ3" s="18"/>
-      <c r="BA3" s="18"/>
-      <c r="BB3" s="19"/>
-      <c r="BC3" s="36" t="s">
+      <c r="AA3" s="47"/>
+      <c r="AB3" s="47"/>
+      <c r="AC3" s="47"/>
+      <c r="AD3" s="47"/>
+      <c r="AE3" s="47"/>
+      <c r="AF3" s="47"/>
+      <c r="AG3" s="47"/>
+      <c r="AH3" s="47"/>
+      <c r="AI3" s="47"/>
+      <c r="AJ3" s="47"/>
+      <c r="AK3" s="47"/>
+      <c r="AL3" s="47"/>
+      <c r="AM3" s="47"/>
+      <c r="AN3" s="47"/>
+      <c r="AO3" s="47"/>
+      <c r="AP3" s="47"/>
+      <c r="AQ3" s="47"/>
+      <c r="AR3" s="47"/>
+      <c r="AS3" s="47"/>
+      <c r="AT3" s="47"/>
+      <c r="AU3" s="47"/>
+      <c r="AV3" s="47"/>
+      <c r="AW3" s="47"/>
+      <c r="AX3" s="47"/>
+      <c r="AY3" s="47"/>
+      <c r="AZ3" s="47"/>
+      <c r="BA3" s="47"/>
+      <c r="BB3" s="48"/>
+      <c r="BC3" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="BD3" s="37"/>
-      <c r="BE3" s="37"/>
-      <c r="BF3" s="37"/>
-      <c r="BG3" s="37"/>
-      <c r="BH3" s="37"/>
-      <c r="BI3" s="37"/>
-      <c r="BJ3" s="37"/>
-      <c r="BK3" s="37"/>
-      <c r="BL3" s="37"/>
-      <c r="BM3" s="37"/>
-      <c r="BN3" s="38"/>
-      <c r="BO3" s="28" t="s">
+      <c r="BD3" s="66"/>
+      <c r="BE3" s="66"/>
+      <c r="BF3" s="66"/>
+      <c r="BG3" s="66"/>
+      <c r="BH3" s="66"/>
+      <c r="BI3" s="66"/>
+      <c r="BJ3" s="66"/>
+      <c r="BK3" s="66"/>
+      <c r="BL3" s="66"/>
+      <c r="BM3" s="66"/>
+      <c r="BN3" s="67"/>
+      <c r="BO3" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="BP3" s="29"/>
-      <c r="BQ3" s="29"/>
-      <c r="BR3" s="29"/>
-      <c r="BS3" s="29"/>
-      <c r="BT3" s="29"/>
-      <c r="BU3" s="29"/>
-      <c r="BV3" s="29"/>
-      <c r="BW3" s="29"/>
-      <c r="BX3" s="29"/>
-      <c r="BY3" s="29"/>
-      <c r="BZ3" s="30"/>
+      <c r="BP3" s="53"/>
+      <c r="BQ3" s="53"/>
+      <c r="BR3" s="53"/>
+      <c r="BS3" s="53"/>
+      <c r="BT3" s="53"/>
+      <c r="BU3" s="53"/>
+      <c r="BV3" s="53"/>
+      <c r="BW3" s="53"/>
+      <c r="BX3" s="53"/>
+      <c r="BY3" s="53"/>
+      <c r="BZ3" s="54"/>
     </row>
     <row r="4" spans="1:82" s="1" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="33"/>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41"/>
-      <c r="J4" s="41"/>
-      <c r="K4" s="41"/>
-      <c r="L4" s="41"/>
-      <c r="M4" s="60"/>
-      <c r="N4" s="33"/>
-      <c r="O4" s="41"/>
-      <c r="P4" s="45"/>
-      <c r="Q4" s="45"/>
-      <c r="R4" s="45"/>
-      <c r="S4" s="45"/>
-      <c r="T4" s="45"/>
-      <c r="U4" s="45"/>
-      <c r="V4" s="45"/>
-      <c r="W4" s="45"/>
-      <c r="X4" s="45"/>
-      <c r="Y4" s="23"/>
-      <c r="Z4" s="24"/>
-      <c r="AA4" s="25"/>
-      <c r="AB4" s="25"/>
-      <c r="AC4" s="25"/>
-      <c r="AD4" s="25"/>
-      <c r="AE4" s="25"/>
-      <c r="AF4" s="25"/>
-      <c r="AG4" s="25"/>
-      <c r="AH4" s="25"/>
-      <c r="AI4" s="25"/>
-      <c r="AJ4" s="25"/>
-      <c r="AK4" s="25"/>
-      <c r="AL4" s="25"/>
-      <c r="AM4" s="25"/>
-      <c r="AN4" s="25"/>
-      <c r="AO4" s="25"/>
-      <c r="AP4" s="25"/>
-      <c r="AQ4" s="25"/>
-      <c r="AR4" s="25"/>
-      <c r="AS4" s="25"/>
-      <c r="AT4" s="25"/>
-      <c r="AU4" s="25"/>
-      <c r="AV4" s="25"/>
-      <c r="AW4" s="25"/>
-      <c r="AX4" s="25"/>
-      <c r="AY4" s="25"/>
-      <c r="AZ4" s="25"/>
-      <c r="BA4" s="25"/>
-      <c r="BB4" s="26"/>
-      <c r="BC4" s="36" t="s">
+      <c r="A4" s="69"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="76"/>
+      <c r="K4" s="76"/>
+      <c r="L4" s="76"/>
+      <c r="M4" s="77"/>
+      <c r="N4" s="69"/>
+      <c r="O4" s="76"/>
+      <c r="P4" s="89"/>
+      <c r="Q4" s="89"/>
+      <c r="R4" s="89"/>
+      <c r="S4" s="89"/>
+      <c r="T4" s="89"/>
+      <c r="U4" s="89"/>
+      <c r="V4" s="89"/>
+      <c r="W4" s="89"/>
+      <c r="X4" s="89"/>
+      <c r="Y4" s="59"/>
+      <c r="Z4" s="49"/>
+      <c r="AA4" s="50"/>
+      <c r="AB4" s="50"/>
+      <c r="AC4" s="50"/>
+      <c r="AD4" s="50"/>
+      <c r="AE4" s="50"/>
+      <c r="AF4" s="50"/>
+      <c r="AG4" s="50"/>
+      <c r="AH4" s="50"/>
+      <c r="AI4" s="50"/>
+      <c r="AJ4" s="50"/>
+      <c r="AK4" s="50"/>
+      <c r="AL4" s="50"/>
+      <c r="AM4" s="50"/>
+      <c r="AN4" s="50"/>
+      <c r="AO4" s="50"/>
+      <c r="AP4" s="50"/>
+      <c r="AQ4" s="50"/>
+      <c r="AR4" s="50"/>
+      <c r="AS4" s="50"/>
+      <c r="AT4" s="50"/>
+      <c r="AU4" s="50"/>
+      <c r="AV4" s="50"/>
+      <c r="AW4" s="50"/>
+      <c r="AX4" s="50"/>
+      <c r="AY4" s="50"/>
+      <c r="AZ4" s="50"/>
+      <c r="BA4" s="50"/>
+      <c r="BB4" s="51"/>
+      <c r="BC4" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="BD4" s="37"/>
-      <c r="BE4" s="37"/>
-      <c r="BF4" s="37"/>
-      <c r="BG4" s="37"/>
-      <c r="BH4" s="37"/>
-      <c r="BI4" s="37"/>
-      <c r="BJ4" s="37"/>
-      <c r="BK4" s="37"/>
-      <c r="BL4" s="37"/>
-      <c r="BM4" s="37"/>
-      <c r="BN4" s="38"/>
-      <c r="BO4" s="28" t="s">
+      <c r="BD4" s="66"/>
+      <c r="BE4" s="66"/>
+      <c r="BF4" s="66"/>
+      <c r="BG4" s="66"/>
+      <c r="BH4" s="66"/>
+      <c r="BI4" s="66"/>
+      <c r="BJ4" s="66"/>
+      <c r="BK4" s="66"/>
+      <c r="BL4" s="66"/>
+      <c r="BM4" s="66"/>
+      <c r="BN4" s="67"/>
+      <c r="BO4" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="BP4" s="29"/>
-      <c r="BQ4" s="29"/>
-      <c r="BR4" s="29"/>
-      <c r="BS4" s="29"/>
-      <c r="BT4" s="29"/>
-      <c r="BU4" s="29"/>
-      <c r="BV4" s="29"/>
-      <c r="BW4" s="29"/>
-      <c r="BX4" s="29"/>
-      <c r="BY4" s="29"/>
-      <c r="BZ4" s="30"/>
+      <c r="BP4" s="53"/>
+      <c r="BQ4" s="53"/>
+      <c r="BR4" s="53"/>
+      <c r="BS4" s="53"/>
+      <c r="BT4" s="53"/>
+      <c r="BU4" s="53"/>
+      <c r="BV4" s="53"/>
+      <c r="BW4" s="53"/>
+      <c r="BX4" s="53"/>
+      <c r="BY4" s="53"/>
+      <c r="BZ4" s="54"/>
     </row>
     <row r="5" spans="1:82" s="1" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="34"/>
-      <c r="B5" s="46"/>
-      <c r="C5" s="46"/>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="46"/>
-      <c r="J5" s="46"/>
-      <c r="K5" s="46"/>
-      <c r="L5" s="46"/>
-      <c r="M5" s="61"/>
-      <c r="N5" s="34"/>
-      <c r="O5" s="46"/>
-      <c r="P5" s="25"/>
-      <c r="Q5" s="25"/>
-      <c r="R5" s="25"/>
-      <c r="S5" s="25"/>
-      <c r="T5" s="25"/>
-      <c r="U5" s="25"/>
-      <c r="V5" s="25"/>
-      <c r="W5" s="25"/>
-      <c r="X5" s="25"/>
-      <c r="Y5" s="26"/>
-      <c r="Z5" s="42" t="s">
+      <c r="A5" s="70"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="78"/>
+      <c r="K5" s="78"/>
+      <c r="L5" s="78"/>
+      <c r="M5" s="79"/>
+      <c r="N5" s="70"/>
+      <c r="O5" s="78"/>
+      <c r="P5" s="50"/>
+      <c r="Q5" s="50"/>
+      <c r="R5" s="50"/>
+      <c r="S5" s="50"/>
+      <c r="T5" s="50"/>
+      <c r="U5" s="50"/>
+      <c r="V5" s="50"/>
+      <c r="W5" s="50"/>
+      <c r="X5" s="50"/>
+      <c r="Y5" s="51"/>
+      <c r="Z5" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="AA5" s="18"/>
-      <c r="AB5" s="18"/>
-      <c r="AC5" s="18"/>
-      <c r="AD5" s="18"/>
-      <c r="AE5" s="18"/>
-      <c r="AF5" s="18"/>
-      <c r="AG5" s="18"/>
-      <c r="AH5" s="18"/>
-      <c r="AI5" s="18"/>
-      <c r="AJ5" s="18"/>
-      <c r="AK5" s="18"/>
-      <c r="AL5" s="18"/>
-      <c r="AM5" s="18"/>
-      <c r="AN5" s="18"/>
-      <c r="AO5" s="18"/>
-      <c r="AP5" s="18"/>
-      <c r="AQ5" s="18"/>
-      <c r="AR5" s="18"/>
-      <c r="AS5" s="18"/>
-      <c r="AT5" s="18"/>
-      <c r="AU5" s="18"/>
-      <c r="AV5" s="18"/>
-      <c r="AW5" s="18"/>
-      <c r="AX5" s="18"/>
-      <c r="AY5" s="18"/>
-      <c r="AZ5" s="18"/>
-      <c r="BA5" s="18"/>
-      <c r="BB5" s="19"/>
-      <c r="BC5" s="36" t="s">
+      <c r="AA5" s="47"/>
+      <c r="AB5" s="47"/>
+      <c r="AC5" s="47"/>
+      <c r="AD5" s="47"/>
+      <c r="AE5" s="47"/>
+      <c r="AF5" s="47"/>
+      <c r="AG5" s="47"/>
+      <c r="AH5" s="47"/>
+      <c r="AI5" s="47"/>
+      <c r="AJ5" s="47"/>
+      <c r="AK5" s="47"/>
+      <c r="AL5" s="47"/>
+      <c r="AM5" s="47"/>
+      <c r="AN5" s="47"/>
+      <c r="AO5" s="47"/>
+      <c r="AP5" s="47"/>
+      <c r="AQ5" s="47"/>
+      <c r="AR5" s="47"/>
+      <c r="AS5" s="47"/>
+      <c r="AT5" s="47"/>
+      <c r="AU5" s="47"/>
+      <c r="AV5" s="47"/>
+      <c r="AW5" s="47"/>
+      <c r="AX5" s="47"/>
+      <c r="AY5" s="47"/>
+      <c r="AZ5" s="47"/>
+      <c r="BA5" s="47"/>
+      <c r="BB5" s="48"/>
+      <c r="BC5" s="65" t="s">
         <v>14</v>
       </c>
-      <c r="BD5" s="37"/>
-      <c r="BE5" s="37"/>
-      <c r="BF5" s="37"/>
-      <c r="BG5" s="37"/>
-      <c r="BH5" s="37"/>
-      <c r="BI5" s="37"/>
-      <c r="BJ5" s="37"/>
-      <c r="BK5" s="37"/>
-      <c r="BL5" s="37"/>
-      <c r="BM5" s="37"/>
-      <c r="BN5" s="38"/>
-      <c r="BO5" s="28" t="s">
+      <c r="BD5" s="66"/>
+      <c r="BE5" s="66"/>
+      <c r="BF5" s="66"/>
+      <c r="BG5" s="66"/>
+      <c r="BH5" s="66"/>
+      <c r="BI5" s="66"/>
+      <c r="BJ5" s="66"/>
+      <c r="BK5" s="66"/>
+      <c r="BL5" s="66"/>
+      <c r="BM5" s="66"/>
+      <c r="BN5" s="67"/>
+      <c r="BO5" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="BP5" s="29"/>
-      <c r="BQ5" s="29"/>
-      <c r="BR5" s="29"/>
-      <c r="BS5" s="29"/>
-      <c r="BT5" s="29"/>
-      <c r="BU5" s="29"/>
-      <c r="BV5" s="29"/>
-      <c r="BW5" s="29"/>
-      <c r="BX5" s="29"/>
-      <c r="BY5" s="29"/>
-      <c r="BZ5" s="30"/>
+      <c r="BP5" s="53"/>
+      <c r="BQ5" s="53"/>
+      <c r="BR5" s="53"/>
+      <c r="BS5" s="53"/>
+      <c r="BT5" s="53"/>
+      <c r="BU5" s="53"/>
+      <c r="BV5" s="53"/>
+      <c r="BW5" s="53"/>
+      <c r="BX5" s="53"/>
+      <c r="BY5" s="53"/>
+      <c r="BZ5" s="54"/>
     </row>
     <row r="6" spans="1:82" s="1" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="52"/>
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52"/>
-      <c r="F6" s="52"/>
-      <c r="G6" s="52"/>
-      <c r="H6" s="52"/>
-      <c r="I6" s="52"/>
-      <c r="J6" s="52"/>
-      <c r="K6" s="52"/>
-      <c r="L6" s="52"/>
-      <c r="M6" s="54"/>
-      <c r="N6" s="51" t="s">
+      <c r="B6" s="63"/>
+      <c r="C6" s="63"/>
+      <c r="D6" s="63"/>
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="63"/>
+      <c r="L6" s="63"/>
+      <c r="M6" s="64"/>
+      <c r="N6" s="62" t="s">
         <v>17</v>
       </c>
-      <c r="O6" s="52"/>
-      <c r="P6" s="37"/>
-      <c r="Q6" s="37"/>
-      <c r="R6" s="37"/>
-      <c r="S6" s="37"/>
-      <c r="T6" s="37"/>
-      <c r="U6" s="37"/>
-      <c r="V6" s="37"/>
-      <c r="W6" s="37"/>
-      <c r="X6" s="37"/>
-      <c r="Y6" s="38"/>
-      <c r="Z6" s="24"/>
-      <c r="AA6" s="25"/>
-      <c r="AB6" s="25"/>
-      <c r="AC6" s="25"/>
-      <c r="AD6" s="25"/>
-      <c r="AE6" s="25"/>
-      <c r="AF6" s="25"/>
-      <c r="AG6" s="25"/>
-      <c r="AH6" s="25"/>
-      <c r="AI6" s="25"/>
-      <c r="AJ6" s="25"/>
-      <c r="AK6" s="25"/>
-      <c r="AL6" s="25"/>
-      <c r="AM6" s="25"/>
-      <c r="AN6" s="25"/>
-      <c r="AO6" s="25"/>
-      <c r="AP6" s="25"/>
-      <c r="AQ6" s="25"/>
-      <c r="AR6" s="25"/>
-      <c r="AS6" s="25"/>
-      <c r="AT6" s="25"/>
-      <c r="AU6" s="25"/>
-      <c r="AV6" s="25"/>
-      <c r="AW6" s="25"/>
-      <c r="AX6" s="25"/>
-      <c r="AY6" s="25"/>
-      <c r="AZ6" s="25"/>
-      <c r="BA6" s="25"/>
-      <c r="BB6" s="26"/>
-      <c r="BC6" s="36" t="s">
+      <c r="O6" s="63"/>
+      <c r="P6" s="66"/>
+      <c r="Q6" s="66"/>
+      <c r="R6" s="66"/>
+      <c r="S6" s="66"/>
+      <c r="T6" s="66"/>
+      <c r="U6" s="66"/>
+      <c r="V6" s="66"/>
+      <c r="W6" s="66"/>
+      <c r="X6" s="66"/>
+      <c r="Y6" s="67"/>
+      <c r="Z6" s="49"/>
+      <c r="AA6" s="50"/>
+      <c r="AB6" s="50"/>
+      <c r="AC6" s="50"/>
+      <c r="AD6" s="50"/>
+      <c r="AE6" s="50"/>
+      <c r="AF6" s="50"/>
+      <c r="AG6" s="50"/>
+      <c r="AH6" s="50"/>
+      <c r="AI6" s="50"/>
+      <c r="AJ6" s="50"/>
+      <c r="AK6" s="50"/>
+      <c r="AL6" s="50"/>
+      <c r="AM6" s="50"/>
+      <c r="AN6" s="50"/>
+      <c r="AO6" s="50"/>
+      <c r="AP6" s="50"/>
+      <c r="AQ6" s="50"/>
+      <c r="AR6" s="50"/>
+      <c r="AS6" s="50"/>
+      <c r="AT6" s="50"/>
+      <c r="AU6" s="50"/>
+      <c r="AV6" s="50"/>
+      <c r="AW6" s="50"/>
+      <c r="AX6" s="50"/>
+      <c r="AY6" s="50"/>
+      <c r="AZ6" s="50"/>
+      <c r="BA6" s="50"/>
+      <c r="BB6" s="51"/>
+      <c r="BC6" s="65" t="s">
         <v>18</v>
       </c>
-      <c r="BD6" s="37"/>
-      <c r="BE6" s="37"/>
-      <c r="BF6" s="37"/>
-      <c r="BG6" s="37"/>
-      <c r="BH6" s="37"/>
-      <c r="BI6" s="37"/>
-      <c r="BJ6" s="37"/>
-      <c r="BK6" s="37"/>
-      <c r="BL6" s="37"/>
-      <c r="BM6" s="37"/>
-      <c r="BN6" s="38"/>
-      <c r="BO6" s="28" t="s">
+      <c r="BD6" s="66"/>
+      <c r="BE6" s="66"/>
+      <c r="BF6" s="66"/>
+      <c r="BG6" s="66"/>
+      <c r="BH6" s="66"/>
+      <c r="BI6" s="66"/>
+      <c r="BJ6" s="66"/>
+      <c r="BK6" s="66"/>
+      <c r="BL6" s="66"/>
+      <c r="BM6" s="66"/>
+      <c r="BN6" s="67"/>
+      <c r="BO6" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="BP6" s="29"/>
-      <c r="BQ6" s="29"/>
-      <c r="BR6" s="29"/>
-      <c r="BS6" s="29"/>
-      <c r="BT6" s="29"/>
-      <c r="BU6" s="29"/>
-      <c r="BV6" s="29"/>
-      <c r="BW6" s="29"/>
-      <c r="BX6" s="29"/>
-      <c r="BY6" s="29"/>
-      <c r="BZ6" s="30"/>
+      <c r="BP6" s="53"/>
+      <c r="BQ6" s="53"/>
+      <c r="BR6" s="53"/>
+      <c r="BS6" s="53"/>
+      <c r="BT6" s="53"/>
+      <c r="BU6" s="53"/>
+      <c r="BV6" s="53"/>
+      <c r="BW6" s="53"/>
+      <c r="BX6" s="53"/>
+      <c r="BY6" s="53"/>
+      <c r="BZ6" s="54"/>
     </row>
     <row r="7" spans="1:82" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="13"/>
@@ -2552,54 +2592,54 @@
       <c r="O21" s="14"/>
       <c r="P21" s="3"/>
       <c r="Q21" s="3"/>
-      <c r="R21" s="53" t="s">
+      <c r="R21" s="60" t="s">
         <v>20</v>
       </c>
-      <c r="S21" s="18"/>
-      <c r="T21" s="18"/>
-      <c r="U21" s="18"/>
-      <c r="V21" s="18"/>
-      <c r="W21" s="18"/>
-      <c r="X21" s="18"/>
-      <c r="Y21" s="18"/>
-      <c r="Z21" s="18"/>
-      <c r="AA21" s="18"/>
-      <c r="AB21" s="18"/>
-      <c r="AC21" s="18"/>
-      <c r="AD21" s="18"/>
-      <c r="AE21" s="19"/>
-      <c r="AF21" s="53" t="s">
+      <c r="S21" s="47"/>
+      <c r="T21" s="47"/>
+      <c r="U21" s="47"/>
+      <c r="V21" s="47"/>
+      <c r="W21" s="47"/>
+      <c r="X21" s="47"/>
+      <c r="Y21" s="47"/>
+      <c r="Z21" s="47"/>
+      <c r="AA21" s="47"/>
+      <c r="AB21" s="47"/>
+      <c r="AC21" s="47"/>
+      <c r="AD21" s="47"/>
+      <c r="AE21" s="48"/>
+      <c r="AF21" s="60" t="s">
         <v>21</v>
       </c>
-      <c r="AG21" s="18"/>
-      <c r="AH21" s="18"/>
-      <c r="AI21" s="18"/>
-      <c r="AJ21" s="18"/>
-      <c r="AK21" s="18"/>
-      <c r="AL21" s="18"/>
-      <c r="AM21" s="18"/>
-      <c r="AN21" s="18"/>
-      <c r="AO21" s="18"/>
-      <c r="AP21" s="18"/>
-      <c r="AQ21" s="18"/>
-      <c r="AR21" s="18"/>
-      <c r="AS21" s="19"/>
-      <c r="AT21" s="53" t="s">
+      <c r="AG21" s="47"/>
+      <c r="AH21" s="47"/>
+      <c r="AI21" s="47"/>
+      <c r="AJ21" s="47"/>
+      <c r="AK21" s="47"/>
+      <c r="AL21" s="47"/>
+      <c r="AM21" s="47"/>
+      <c r="AN21" s="47"/>
+      <c r="AO21" s="47"/>
+      <c r="AP21" s="47"/>
+      <c r="AQ21" s="47"/>
+      <c r="AR21" s="47"/>
+      <c r="AS21" s="48"/>
+      <c r="AT21" s="60" t="s">
         <v>22</v>
       </c>
-      <c r="AU21" s="18"/>
-      <c r="AV21" s="18"/>
-      <c r="AW21" s="18"/>
-      <c r="AX21" s="18"/>
-      <c r="AY21" s="18"/>
-      <c r="AZ21" s="18"/>
-      <c r="BA21" s="18"/>
-      <c r="BB21" s="18"/>
-      <c r="BC21" s="18"/>
-      <c r="BD21" s="18"/>
-      <c r="BE21" s="18"/>
-      <c r="BF21" s="18"/>
-      <c r="BG21" s="19"/>
+      <c r="AU21" s="47"/>
+      <c r="AV21" s="47"/>
+      <c r="AW21" s="47"/>
+      <c r="AX21" s="47"/>
+      <c r="AY21" s="47"/>
+      <c r="AZ21" s="47"/>
+      <c r="BA21" s="47"/>
+      <c r="BB21" s="47"/>
+      <c r="BC21" s="47"/>
+      <c r="BD21" s="47"/>
+      <c r="BE21" s="47"/>
+      <c r="BF21" s="47"/>
+      <c r="BG21" s="48"/>
     </row>
     <row r="22" spans="1:82" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="13"/>
@@ -2619,48 +2659,48 @@
       <c r="O22" s="14"/>
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
-      <c r="R22" s="20"/>
-      <c r="S22" s="22"/>
-      <c r="T22" s="22"/>
-      <c r="U22" s="22"/>
-      <c r="V22" s="22"/>
-      <c r="W22" s="22"/>
-      <c r="X22" s="22"/>
-      <c r="Y22" s="22"/>
-      <c r="Z22" s="22"/>
-      <c r="AA22" s="22"/>
-      <c r="AB22" s="22"/>
-      <c r="AC22" s="22"/>
-      <c r="AD22" s="22"/>
-      <c r="AE22" s="23"/>
-      <c r="AF22" s="20"/>
-      <c r="AG22" s="22"/>
-      <c r="AH22" s="22"/>
-      <c r="AI22" s="22"/>
-      <c r="AJ22" s="22"/>
-      <c r="AK22" s="22"/>
-      <c r="AL22" s="22"/>
-      <c r="AM22" s="22"/>
-      <c r="AN22" s="22"/>
-      <c r="AO22" s="22"/>
-      <c r="AP22" s="22"/>
-      <c r="AQ22" s="22"/>
-      <c r="AR22" s="22"/>
-      <c r="AS22" s="23"/>
-      <c r="AT22" s="20"/>
-      <c r="AU22" s="22"/>
-      <c r="AV22" s="22"/>
-      <c r="AW22" s="21"/>
-      <c r="AX22" s="21"/>
-      <c r="AY22" s="21"/>
-      <c r="AZ22" s="21"/>
-      <c r="BA22" s="21"/>
-      <c r="BB22" s="22"/>
-      <c r="BC22" s="22"/>
-      <c r="BD22" s="22"/>
-      <c r="BE22" s="22"/>
-      <c r="BF22" s="22"/>
-      <c r="BG22" s="23"/>
+      <c r="R22" s="58"/>
+      <c r="S22" s="56"/>
+      <c r="T22" s="56"/>
+      <c r="U22" s="56"/>
+      <c r="V22" s="56"/>
+      <c r="W22" s="56"/>
+      <c r="X22" s="56"/>
+      <c r="Y22" s="56"/>
+      <c r="Z22" s="56"/>
+      <c r="AA22" s="56"/>
+      <c r="AB22" s="56"/>
+      <c r="AC22" s="56"/>
+      <c r="AD22" s="56"/>
+      <c r="AE22" s="59"/>
+      <c r="AF22" s="58"/>
+      <c r="AG22" s="56"/>
+      <c r="AH22" s="56"/>
+      <c r="AI22" s="56"/>
+      <c r="AJ22" s="56"/>
+      <c r="AK22" s="56"/>
+      <c r="AL22" s="56"/>
+      <c r="AM22" s="56"/>
+      <c r="AN22" s="56"/>
+      <c r="AO22" s="56"/>
+      <c r="AP22" s="56"/>
+      <c r="AQ22" s="56"/>
+      <c r="AR22" s="56"/>
+      <c r="AS22" s="59"/>
+      <c r="AT22" s="58"/>
+      <c r="AU22" s="56"/>
+      <c r="AV22" s="56"/>
+      <c r="AW22" s="61"/>
+      <c r="AX22" s="61"/>
+      <c r="AY22" s="61"/>
+      <c r="AZ22" s="61"/>
+      <c r="BA22" s="61"/>
+      <c r="BB22" s="56"/>
+      <c r="BC22" s="56"/>
+      <c r="BD22" s="56"/>
+      <c r="BE22" s="56"/>
+      <c r="BF22" s="56"/>
+      <c r="BG22" s="59"/>
     </row>
     <row r="23" spans="1:82" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="13"/>
@@ -2680,48 +2720,48 @@
       <c r="O23" s="14"/>
       <c r="P23" s="3"/>
       <c r="Q23" s="3"/>
-      <c r="R23" s="24"/>
-      <c r="S23" s="25"/>
-      <c r="T23" s="25"/>
-      <c r="U23" s="25"/>
-      <c r="V23" s="25"/>
-      <c r="W23" s="25"/>
-      <c r="X23" s="25"/>
-      <c r="Y23" s="25"/>
-      <c r="Z23" s="25"/>
-      <c r="AA23" s="25"/>
-      <c r="AB23" s="25"/>
-      <c r="AC23" s="25"/>
-      <c r="AD23" s="25"/>
-      <c r="AE23" s="26"/>
-      <c r="AF23" s="24"/>
-      <c r="AG23" s="25"/>
-      <c r="AH23" s="25"/>
-      <c r="AI23" s="25"/>
-      <c r="AJ23" s="25"/>
-      <c r="AK23" s="25"/>
-      <c r="AL23" s="25"/>
-      <c r="AM23" s="25"/>
-      <c r="AN23" s="25"/>
-      <c r="AO23" s="25"/>
-      <c r="AP23" s="25"/>
-      <c r="AQ23" s="25"/>
-      <c r="AR23" s="25"/>
-      <c r="AS23" s="26"/>
-      <c r="AT23" s="24"/>
-      <c r="AU23" s="25"/>
-      <c r="AV23" s="25"/>
-      <c r="AW23" s="25"/>
-      <c r="AX23" s="25"/>
-      <c r="AY23" s="25"/>
-      <c r="AZ23" s="25"/>
-      <c r="BA23" s="25"/>
-      <c r="BB23" s="25"/>
-      <c r="BC23" s="25"/>
-      <c r="BD23" s="25"/>
-      <c r="BE23" s="25"/>
-      <c r="BF23" s="25"/>
-      <c r="BG23" s="26"/>
+      <c r="R23" s="49"/>
+      <c r="S23" s="50"/>
+      <c r="T23" s="50"/>
+      <c r="U23" s="50"/>
+      <c r="V23" s="50"/>
+      <c r="W23" s="50"/>
+      <c r="X23" s="50"/>
+      <c r="Y23" s="50"/>
+      <c r="Z23" s="50"/>
+      <c r="AA23" s="50"/>
+      <c r="AB23" s="50"/>
+      <c r="AC23" s="50"/>
+      <c r="AD23" s="50"/>
+      <c r="AE23" s="51"/>
+      <c r="AF23" s="49"/>
+      <c r="AG23" s="50"/>
+      <c r="AH23" s="50"/>
+      <c r="AI23" s="50"/>
+      <c r="AJ23" s="50"/>
+      <c r="AK23" s="50"/>
+      <c r="AL23" s="50"/>
+      <c r="AM23" s="50"/>
+      <c r="AN23" s="50"/>
+      <c r="AO23" s="50"/>
+      <c r="AP23" s="50"/>
+      <c r="AQ23" s="50"/>
+      <c r="AR23" s="50"/>
+      <c r="AS23" s="51"/>
+      <c r="AT23" s="49"/>
+      <c r="AU23" s="50"/>
+      <c r="AV23" s="50"/>
+      <c r="AW23" s="50"/>
+      <c r="AX23" s="50"/>
+      <c r="AY23" s="50"/>
+      <c r="AZ23" s="50"/>
+      <c r="BA23" s="50"/>
+      <c r="BB23" s="50"/>
+      <c r="BC23" s="50"/>
+      <c r="BD23" s="50"/>
+      <c r="BE23" s="50"/>
+      <c r="BF23" s="50"/>
+      <c r="BG23" s="51"/>
     </row>
     <row r="24" spans="1:82" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="13"/>
@@ -2741,50 +2781,50 @@
       <c r="O24" s="14"/>
       <c r="P24" s="3"/>
       <c r="Q24" s="3"/>
-      <c r="R24" s="47" t="s">
+      <c r="R24" s="90" t="s">
         <v>12</v>
       </c>
-      <c r="S24" s="18"/>
-      <c r="T24" s="18"/>
-      <c r="U24" s="18"/>
-      <c r="V24" s="18"/>
-      <c r="W24" s="18"/>
-      <c r="X24" s="18"/>
-      <c r="Y24" s="18"/>
-      <c r="Z24" s="18"/>
-      <c r="AA24" s="18"/>
-      <c r="AB24" s="18"/>
-      <c r="AC24" s="18"/>
-      <c r="AD24" s="18"/>
-      <c r="AE24" s="19"/>
-      <c r="AF24" s="35"/>
-      <c r="AG24" s="18"/>
-      <c r="AH24" s="18"/>
-      <c r="AI24" s="18"/>
-      <c r="AJ24" s="18"/>
-      <c r="AK24" s="18"/>
-      <c r="AL24" s="18"/>
-      <c r="AM24" s="18"/>
-      <c r="AN24" s="18"/>
-      <c r="AO24" s="18"/>
-      <c r="AP24" s="18"/>
-      <c r="AQ24" s="18"/>
-      <c r="AR24" s="18"/>
-      <c r="AS24" s="19"/>
-      <c r="AT24" s="35"/>
-      <c r="AU24" s="18"/>
-      <c r="AV24" s="18"/>
-      <c r="AW24" s="18"/>
-      <c r="AX24" s="18"/>
-      <c r="AY24" s="18"/>
-      <c r="AZ24" s="18"/>
-      <c r="BA24" s="18"/>
-      <c r="BB24" s="18"/>
-      <c r="BC24" s="18"/>
-      <c r="BD24" s="18"/>
-      <c r="BE24" s="18"/>
-      <c r="BF24" s="18"/>
-      <c r="BG24" s="19"/>
+      <c r="S24" s="47"/>
+      <c r="T24" s="47"/>
+      <c r="U24" s="47"/>
+      <c r="V24" s="47"/>
+      <c r="W24" s="47"/>
+      <c r="X24" s="47"/>
+      <c r="Y24" s="47"/>
+      <c r="Z24" s="47"/>
+      <c r="AA24" s="47"/>
+      <c r="AB24" s="47"/>
+      <c r="AC24" s="47"/>
+      <c r="AD24" s="47"/>
+      <c r="AE24" s="48"/>
+      <c r="AF24" s="71"/>
+      <c r="AG24" s="47"/>
+      <c r="AH24" s="47"/>
+      <c r="AI24" s="47"/>
+      <c r="AJ24" s="47"/>
+      <c r="AK24" s="47"/>
+      <c r="AL24" s="47"/>
+      <c r="AM24" s="47"/>
+      <c r="AN24" s="47"/>
+      <c r="AO24" s="47"/>
+      <c r="AP24" s="47"/>
+      <c r="AQ24" s="47"/>
+      <c r="AR24" s="47"/>
+      <c r="AS24" s="48"/>
+      <c r="AT24" s="71"/>
+      <c r="AU24" s="47"/>
+      <c r="AV24" s="47"/>
+      <c r="AW24" s="47"/>
+      <c r="AX24" s="47"/>
+      <c r="AY24" s="47"/>
+      <c r="AZ24" s="47"/>
+      <c r="BA24" s="47"/>
+      <c r="BB24" s="47"/>
+      <c r="BC24" s="47"/>
+      <c r="BD24" s="47"/>
+      <c r="BE24" s="47"/>
+      <c r="BF24" s="47"/>
+      <c r="BG24" s="48"/>
     </row>
     <row r="25" spans="1:82" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="13"/>
@@ -2804,48 +2844,48 @@
       <c r="O25" s="14"/>
       <c r="P25" s="3"/>
       <c r="Q25" s="3"/>
-      <c r="R25" s="20"/>
-      <c r="S25" s="22"/>
-      <c r="T25" s="22"/>
-      <c r="U25" s="22"/>
-      <c r="V25" s="22"/>
-      <c r="W25" s="22"/>
-      <c r="X25" s="22"/>
-      <c r="Y25" s="22"/>
-      <c r="Z25" s="22"/>
-      <c r="AA25" s="22"/>
-      <c r="AB25" s="22"/>
-      <c r="AC25" s="22"/>
-      <c r="AD25" s="22"/>
-      <c r="AE25" s="23"/>
-      <c r="AF25" s="20"/>
-      <c r="AG25" s="22"/>
-      <c r="AH25" s="22"/>
-      <c r="AI25" s="22"/>
-      <c r="AJ25" s="22"/>
-      <c r="AK25" s="22"/>
-      <c r="AL25" s="22"/>
-      <c r="AM25" s="22"/>
-      <c r="AN25" s="22"/>
-      <c r="AO25" s="22"/>
-      <c r="AP25" s="22"/>
-      <c r="AQ25" s="22"/>
-      <c r="AR25" s="22"/>
-      <c r="AS25" s="23"/>
-      <c r="AT25" s="20"/>
-      <c r="AU25" s="22"/>
-      <c r="AV25" s="22"/>
-      <c r="AW25" s="21"/>
-      <c r="AX25" s="21"/>
-      <c r="AY25" s="21"/>
-      <c r="AZ25" s="21"/>
-      <c r="BA25" s="21"/>
-      <c r="BB25" s="22"/>
-      <c r="BC25" s="22"/>
-      <c r="BD25" s="22"/>
-      <c r="BE25" s="22"/>
-      <c r="BF25" s="22"/>
-      <c r="BG25" s="23"/>
+      <c r="R25" s="58"/>
+      <c r="S25" s="56"/>
+      <c r="T25" s="56"/>
+      <c r="U25" s="56"/>
+      <c r="V25" s="56"/>
+      <c r="W25" s="56"/>
+      <c r="X25" s="56"/>
+      <c r="Y25" s="56"/>
+      <c r="Z25" s="56"/>
+      <c r="AA25" s="56"/>
+      <c r="AB25" s="56"/>
+      <c r="AC25" s="56"/>
+      <c r="AD25" s="56"/>
+      <c r="AE25" s="59"/>
+      <c r="AF25" s="58"/>
+      <c r="AG25" s="56"/>
+      <c r="AH25" s="56"/>
+      <c r="AI25" s="56"/>
+      <c r="AJ25" s="56"/>
+      <c r="AK25" s="56"/>
+      <c r="AL25" s="56"/>
+      <c r="AM25" s="56"/>
+      <c r="AN25" s="56"/>
+      <c r="AO25" s="56"/>
+      <c r="AP25" s="56"/>
+      <c r="AQ25" s="56"/>
+      <c r="AR25" s="56"/>
+      <c r="AS25" s="59"/>
+      <c r="AT25" s="58"/>
+      <c r="AU25" s="56"/>
+      <c r="AV25" s="56"/>
+      <c r="AW25" s="61"/>
+      <c r="AX25" s="61"/>
+      <c r="AY25" s="61"/>
+      <c r="AZ25" s="61"/>
+      <c r="BA25" s="61"/>
+      <c r="BB25" s="56"/>
+      <c r="BC25" s="56"/>
+      <c r="BD25" s="56"/>
+      <c r="BE25" s="56"/>
+      <c r="BF25" s="56"/>
+      <c r="BG25" s="59"/>
     </row>
     <row r="26" spans="1:82" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="13"/>
@@ -2865,48 +2905,48 @@
       <c r="O26" s="14"/>
       <c r="P26" s="3"/>
       <c r="Q26" s="3"/>
-      <c r="R26" s="24"/>
-      <c r="S26" s="25"/>
-      <c r="T26" s="25"/>
-      <c r="U26" s="25"/>
-      <c r="V26" s="25"/>
-      <c r="W26" s="25"/>
-      <c r="X26" s="25"/>
-      <c r="Y26" s="25"/>
-      <c r="Z26" s="25"/>
-      <c r="AA26" s="25"/>
-      <c r="AB26" s="25"/>
-      <c r="AC26" s="25"/>
-      <c r="AD26" s="25"/>
-      <c r="AE26" s="26"/>
-      <c r="AF26" s="24"/>
-      <c r="AG26" s="25"/>
-      <c r="AH26" s="25"/>
-      <c r="AI26" s="25"/>
-      <c r="AJ26" s="25"/>
-      <c r="AK26" s="25"/>
-      <c r="AL26" s="25"/>
-      <c r="AM26" s="25"/>
-      <c r="AN26" s="25"/>
-      <c r="AO26" s="25"/>
-      <c r="AP26" s="25"/>
-      <c r="AQ26" s="25"/>
-      <c r="AR26" s="25"/>
-      <c r="AS26" s="26"/>
-      <c r="AT26" s="24"/>
-      <c r="AU26" s="25"/>
-      <c r="AV26" s="25"/>
-      <c r="AW26" s="25"/>
-      <c r="AX26" s="25"/>
-      <c r="AY26" s="25"/>
-      <c r="AZ26" s="25"/>
-      <c r="BA26" s="25"/>
-      <c r="BB26" s="25"/>
-      <c r="BC26" s="25"/>
-      <c r="BD26" s="25"/>
-      <c r="BE26" s="25"/>
-      <c r="BF26" s="25"/>
-      <c r="BG26" s="26"/>
+      <c r="R26" s="49"/>
+      <c r="S26" s="50"/>
+      <c r="T26" s="50"/>
+      <c r="U26" s="50"/>
+      <c r="V26" s="50"/>
+      <c r="W26" s="50"/>
+      <c r="X26" s="50"/>
+      <c r="Y26" s="50"/>
+      <c r="Z26" s="50"/>
+      <c r="AA26" s="50"/>
+      <c r="AB26" s="50"/>
+      <c r="AC26" s="50"/>
+      <c r="AD26" s="50"/>
+      <c r="AE26" s="51"/>
+      <c r="AF26" s="49"/>
+      <c r="AG26" s="50"/>
+      <c r="AH26" s="50"/>
+      <c r="AI26" s="50"/>
+      <c r="AJ26" s="50"/>
+      <c r="AK26" s="50"/>
+      <c r="AL26" s="50"/>
+      <c r="AM26" s="50"/>
+      <c r="AN26" s="50"/>
+      <c r="AO26" s="50"/>
+      <c r="AP26" s="50"/>
+      <c r="AQ26" s="50"/>
+      <c r="AR26" s="50"/>
+      <c r="AS26" s="51"/>
+      <c r="AT26" s="49"/>
+      <c r="AU26" s="50"/>
+      <c r="AV26" s="50"/>
+      <c r="AW26" s="50"/>
+      <c r="AX26" s="50"/>
+      <c r="AY26" s="50"/>
+      <c r="AZ26" s="50"/>
+      <c r="BA26" s="50"/>
+      <c r="BB26" s="50"/>
+      <c r="BC26" s="50"/>
+      <c r="BD26" s="50"/>
+      <c r="BE26" s="50"/>
+      <c r="BF26" s="50"/>
+      <c r="BG26" s="51"/>
     </row>
     <row r="27" spans="1:82" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="13"/>
@@ -2926,57 +2966,57 @@
       <c r="O27" s="14"/>
       <c r="P27" s="3"/>
       <c r="Q27" s="3"/>
-      <c r="R27" s="35" t="str">
+      <c r="R27" s="71" t="str">
         <f>"Fecha :"&amp;BO3</f>
         <v>Fecha :JULIO 23 DEL 2026</v>
       </c>
-      <c r="S27" s="18"/>
-      <c r="T27" s="18"/>
-      <c r="U27" s="18"/>
-      <c r="V27" s="18"/>
-      <c r="W27" s="18"/>
-      <c r="X27" s="18"/>
-      <c r="Y27" s="18"/>
-      <c r="Z27" s="18"/>
-      <c r="AA27" s="18"/>
-      <c r="AB27" s="18"/>
-      <c r="AC27" s="18"/>
-      <c r="AD27" s="18"/>
-      <c r="AE27" s="19"/>
-      <c r="AF27" s="35" t="str">
+      <c r="S27" s="47"/>
+      <c r="T27" s="47"/>
+      <c r="U27" s="47"/>
+      <c r="V27" s="47"/>
+      <c r="W27" s="47"/>
+      <c r="X27" s="47"/>
+      <c r="Y27" s="47"/>
+      <c r="Z27" s="47"/>
+      <c r="AA27" s="47"/>
+      <c r="AB27" s="47"/>
+      <c r="AC27" s="47"/>
+      <c r="AD27" s="47"/>
+      <c r="AE27" s="48"/>
+      <c r="AF27" s="71" t="str">
         <f>"Fecha :"&amp;CC1</f>
         <v>Fecha :JULIO 23 DEL 2026</v>
       </c>
-      <c r="AG27" s="18"/>
-      <c r="AH27" s="18"/>
-      <c r="AI27" s="18"/>
-      <c r="AJ27" s="18"/>
-      <c r="AK27" s="18"/>
-      <c r="AL27" s="18"/>
-      <c r="AM27" s="18"/>
-      <c r="AN27" s="18"/>
-      <c r="AO27" s="18"/>
-      <c r="AP27" s="18"/>
-      <c r="AQ27" s="18"/>
-      <c r="AR27" s="18"/>
-      <c r="AS27" s="19"/>
-      <c r="AT27" s="35" t="str">
+      <c r="AG27" s="47"/>
+      <c r="AH27" s="47"/>
+      <c r="AI27" s="47"/>
+      <c r="AJ27" s="47"/>
+      <c r="AK27" s="47"/>
+      <c r="AL27" s="47"/>
+      <c r="AM27" s="47"/>
+      <c r="AN27" s="47"/>
+      <c r="AO27" s="47"/>
+      <c r="AP27" s="47"/>
+      <c r="AQ27" s="47"/>
+      <c r="AR27" s="47"/>
+      <c r="AS27" s="48"/>
+      <c r="AT27" s="71" t="str">
         <f>"Fecha :"&amp;CC2</f>
         <v>Fecha :JULIO 24 DEL 2026</v>
       </c>
-      <c r="AU27" s="18"/>
-      <c r="AV27" s="18"/>
-      <c r="AW27" s="18"/>
-      <c r="AX27" s="18"/>
-      <c r="AY27" s="18"/>
-      <c r="AZ27" s="18"/>
-      <c r="BA27" s="18"/>
-      <c r="BB27" s="18"/>
-      <c r="BC27" s="18"/>
-      <c r="BD27" s="18"/>
-      <c r="BE27" s="18"/>
-      <c r="BF27" s="18"/>
-      <c r="BG27" s="19"/>
+      <c r="AU27" s="47"/>
+      <c r="AV27" s="47"/>
+      <c r="AW27" s="47"/>
+      <c r="AX27" s="47"/>
+      <c r="AY27" s="47"/>
+      <c r="AZ27" s="47"/>
+      <c r="BA27" s="47"/>
+      <c r="BB27" s="47"/>
+      <c r="BC27" s="47"/>
+      <c r="BD27" s="47"/>
+      <c r="BE27" s="47"/>
+      <c r="BF27" s="47"/>
+      <c r="BG27" s="48"/>
     </row>
     <row r="28" spans="1:82" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="13"/>
@@ -2996,48 +3036,48 @@
       <c r="O28" s="14"/>
       <c r="P28" s="3"/>
       <c r="Q28" s="3"/>
-      <c r="R28" s="20"/>
-      <c r="S28" s="22"/>
-      <c r="T28" s="22"/>
-      <c r="U28" s="22"/>
-      <c r="V28" s="22"/>
-      <c r="W28" s="22"/>
-      <c r="X28" s="22"/>
-      <c r="Y28" s="22"/>
-      <c r="Z28" s="22"/>
-      <c r="AA28" s="22"/>
-      <c r="AB28" s="22"/>
-      <c r="AC28" s="22"/>
-      <c r="AD28" s="22"/>
-      <c r="AE28" s="23"/>
-      <c r="AF28" s="20"/>
-      <c r="AG28" s="22"/>
-      <c r="AH28" s="22"/>
-      <c r="AI28" s="22"/>
-      <c r="AJ28" s="22"/>
-      <c r="AK28" s="22"/>
-      <c r="AL28" s="22"/>
-      <c r="AM28" s="22"/>
-      <c r="AN28" s="22"/>
-      <c r="AO28" s="22"/>
-      <c r="AP28" s="22"/>
-      <c r="AQ28" s="22"/>
-      <c r="AR28" s="22"/>
-      <c r="AS28" s="23"/>
-      <c r="AT28" s="20"/>
-      <c r="AU28" s="22"/>
-      <c r="AV28" s="22"/>
-      <c r="AW28" s="21"/>
-      <c r="AX28" s="21"/>
-      <c r="AY28" s="21"/>
-      <c r="AZ28" s="21"/>
-      <c r="BA28" s="21"/>
-      <c r="BB28" s="22"/>
-      <c r="BC28" s="22"/>
-      <c r="BD28" s="22"/>
-      <c r="BE28" s="22"/>
-      <c r="BF28" s="22"/>
-      <c r="BG28" s="23"/>
+      <c r="R28" s="58"/>
+      <c r="S28" s="56"/>
+      <c r="T28" s="56"/>
+      <c r="U28" s="56"/>
+      <c r="V28" s="56"/>
+      <c r="W28" s="56"/>
+      <c r="X28" s="56"/>
+      <c r="Y28" s="56"/>
+      <c r="Z28" s="56"/>
+      <c r="AA28" s="56"/>
+      <c r="AB28" s="56"/>
+      <c r="AC28" s="56"/>
+      <c r="AD28" s="56"/>
+      <c r="AE28" s="59"/>
+      <c r="AF28" s="58"/>
+      <c r="AG28" s="56"/>
+      <c r="AH28" s="56"/>
+      <c r="AI28" s="56"/>
+      <c r="AJ28" s="56"/>
+      <c r="AK28" s="56"/>
+      <c r="AL28" s="56"/>
+      <c r="AM28" s="56"/>
+      <c r="AN28" s="56"/>
+      <c r="AO28" s="56"/>
+      <c r="AP28" s="56"/>
+      <c r="AQ28" s="56"/>
+      <c r="AR28" s="56"/>
+      <c r="AS28" s="59"/>
+      <c r="AT28" s="58"/>
+      <c r="AU28" s="56"/>
+      <c r="AV28" s="56"/>
+      <c r="AW28" s="61"/>
+      <c r="AX28" s="61"/>
+      <c r="AY28" s="61"/>
+      <c r="AZ28" s="61"/>
+      <c r="BA28" s="61"/>
+      <c r="BB28" s="56"/>
+      <c r="BC28" s="56"/>
+      <c r="BD28" s="56"/>
+      <c r="BE28" s="56"/>
+      <c r="BF28" s="56"/>
+      <c r="BG28" s="59"/>
     </row>
     <row r="29" spans="1:82" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="13"/>
@@ -3057,48 +3097,48 @@
       <c r="O29" s="14"/>
       <c r="P29" s="3"/>
       <c r="Q29" s="3"/>
-      <c r="R29" s="24"/>
-      <c r="S29" s="25"/>
-      <c r="T29" s="25"/>
-      <c r="U29" s="25"/>
-      <c r="V29" s="25"/>
-      <c r="W29" s="25"/>
-      <c r="X29" s="25"/>
-      <c r="Y29" s="25"/>
-      <c r="Z29" s="25"/>
-      <c r="AA29" s="25"/>
-      <c r="AB29" s="25"/>
-      <c r="AC29" s="25"/>
-      <c r="AD29" s="25"/>
-      <c r="AE29" s="26"/>
-      <c r="AF29" s="24"/>
-      <c r="AG29" s="25"/>
-      <c r="AH29" s="25"/>
-      <c r="AI29" s="25"/>
-      <c r="AJ29" s="25"/>
-      <c r="AK29" s="25"/>
-      <c r="AL29" s="25"/>
-      <c r="AM29" s="25"/>
-      <c r="AN29" s="25"/>
-      <c r="AO29" s="25"/>
-      <c r="AP29" s="25"/>
-      <c r="AQ29" s="25"/>
-      <c r="AR29" s="25"/>
-      <c r="AS29" s="26"/>
-      <c r="AT29" s="24"/>
-      <c r="AU29" s="25"/>
-      <c r="AV29" s="25"/>
-      <c r="AW29" s="25"/>
-      <c r="AX29" s="25"/>
-      <c r="AY29" s="25"/>
-      <c r="AZ29" s="25"/>
-      <c r="BA29" s="25"/>
-      <c r="BB29" s="25"/>
-      <c r="BC29" s="25"/>
-      <c r="BD29" s="25"/>
-      <c r="BE29" s="25"/>
-      <c r="BF29" s="25"/>
-      <c r="BG29" s="26"/>
+      <c r="R29" s="49"/>
+      <c r="S29" s="50"/>
+      <c r="T29" s="50"/>
+      <c r="U29" s="50"/>
+      <c r="V29" s="50"/>
+      <c r="W29" s="50"/>
+      <c r="X29" s="50"/>
+      <c r="Y29" s="50"/>
+      <c r="Z29" s="50"/>
+      <c r="AA29" s="50"/>
+      <c r="AB29" s="50"/>
+      <c r="AC29" s="50"/>
+      <c r="AD29" s="50"/>
+      <c r="AE29" s="51"/>
+      <c r="AF29" s="49"/>
+      <c r="AG29" s="50"/>
+      <c r="AH29" s="50"/>
+      <c r="AI29" s="50"/>
+      <c r="AJ29" s="50"/>
+      <c r="AK29" s="50"/>
+      <c r="AL29" s="50"/>
+      <c r="AM29" s="50"/>
+      <c r="AN29" s="50"/>
+      <c r="AO29" s="50"/>
+      <c r="AP29" s="50"/>
+      <c r="AQ29" s="50"/>
+      <c r="AR29" s="50"/>
+      <c r="AS29" s="51"/>
+      <c r="AT29" s="49"/>
+      <c r="AU29" s="50"/>
+      <c r="AV29" s="50"/>
+      <c r="AW29" s="50"/>
+      <c r="AX29" s="50"/>
+      <c r="AY29" s="50"/>
+      <c r="AZ29" s="50"/>
+      <c r="BA29" s="50"/>
+      <c r="BB29" s="50"/>
+      <c r="BC29" s="50"/>
+      <c r="BD29" s="50"/>
+      <c r="BE29" s="50"/>
+      <c r="BF29" s="50"/>
+      <c r="BG29" s="51"/>
     </row>
     <row r="30" spans="1:82" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="13"/>
@@ -3337,22 +3377,22 @@
       <c r="AD36" s="3"/>
       <c r="AE36" s="3"/>
       <c r="AF36" s="3"/>
-      <c r="BK36" s="48"/>
-      <c r="BL36" s="22"/>
-      <c r="BM36" s="22"/>
-      <c r="BN36" s="22"/>
-      <c r="BO36" s="22"/>
-      <c r="BP36" s="22"/>
-      <c r="BQ36" s="22"/>
-      <c r="BR36" s="22"/>
-      <c r="BS36" s="22"/>
-      <c r="BT36" s="22"/>
-      <c r="BU36" s="22"/>
-      <c r="BV36" s="22"/>
-      <c r="BW36" s="22"/>
-      <c r="BX36" s="22"/>
-      <c r="BY36" s="22"/>
-      <c r="BZ36" s="22"/>
+      <c r="BK36" s="91"/>
+      <c r="BL36" s="56"/>
+      <c r="BM36" s="56"/>
+      <c r="BN36" s="56"/>
+      <c r="BO36" s="56"/>
+      <c r="BP36" s="56"/>
+      <c r="BQ36" s="56"/>
+      <c r="BR36" s="56"/>
+      <c r="BS36" s="56"/>
+      <c r="BT36" s="56"/>
+      <c r="BU36" s="56"/>
+      <c r="BV36" s="56"/>
+      <c r="BW36" s="56"/>
+      <c r="BX36" s="56"/>
+      <c r="BY36" s="56"/>
+      <c r="BZ36" s="56"/>
     </row>
     <row r="37" spans="1:78" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="13"/>
@@ -3437,66 +3477,66 @@
       <c r="L39" s="14"/>
       <c r="M39" s="14"/>
       <c r="N39" s="14"/>
-      <c r="O39" s="55" t="s">
+      <c r="O39" s="68" t="s">
         <v>23</v>
       </c>
-      <c r="P39" s="18"/>
-      <c r="Q39" s="18"/>
-      <c r="R39" s="18"/>
-      <c r="S39" s="18"/>
-      <c r="T39" s="18"/>
-      <c r="U39" s="19"/>
-      <c r="V39" s="56" t="s">
+      <c r="P39" s="47"/>
+      <c r="Q39" s="47"/>
+      <c r="R39" s="47"/>
+      <c r="S39" s="47"/>
+      <c r="T39" s="47"/>
+      <c r="U39" s="48"/>
+      <c r="V39" s="57" t="s">
         <v>24</v>
       </c>
-      <c r="W39" s="18"/>
-      <c r="X39" s="18"/>
-      <c r="Y39" s="18"/>
-      <c r="Z39" s="18"/>
-      <c r="AA39" s="18"/>
-      <c r="AB39" s="19"/>
-      <c r="AC39" s="64" t="s">
+      <c r="W39" s="47"/>
+      <c r="X39" s="47"/>
+      <c r="Y39" s="47"/>
+      <c r="Z39" s="47"/>
+      <c r="AA39" s="47"/>
+      <c r="AB39" s="48"/>
+      <c r="AC39" s="82" t="s">
         <v>25</v>
       </c>
-      <c r="AD39" s="18"/>
-      <c r="AE39" s="18"/>
-      <c r="AF39" s="18"/>
-      <c r="AG39" s="18"/>
-      <c r="AH39" s="18"/>
-      <c r="AI39" s="18"/>
-      <c r="AJ39" s="18"/>
-      <c r="AK39" s="18"/>
-      <c r="AL39" s="18"/>
-      <c r="AM39" s="18"/>
-      <c r="AN39" s="18"/>
-      <c r="AO39" s="19"/>
-      <c r="AP39" s="56" t="s">
+      <c r="AD39" s="47"/>
+      <c r="AE39" s="47"/>
+      <c r="AF39" s="47"/>
+      <c r="AG39" s="47"/>
+      <c r="AH39" s="47"/>
+      <c r="AI39" s="47"/>
+      <c r="AJ39" s="47"/>
+      <c r="AK39" s="47"/>
+      <c r="AL39" s="47"/>
+      <c r="AM39" s="47"/>
+      <c r="AN39" s="47"/>
+      <c r="AO39" s="48"/>
+      <c r="AP39" s="57" t="s">
         <v>26</v>
       </c>
-      <c r="AQ39" s="18"/>
-      <c r="AR39" s="18"/>
-      <c r="AS39" s="18"/>
-      <c r="AT39" s="18"/>
-      <c r="AU39" s="18"/>
-      <c r="AV39" s="19"/>
-      <c r="AW39" s="56" t="s">
+      <c r="AQ39" s="47"/>
+      <c r="AR39" s="47"/>
+      <c r="AS39" s="47"/>
+      <c r="AT39" s="47"/>
+      <c r="AU39" s="47"/>
+      <c r="AV39" s="48"/>
+      <c r="AW39" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="AX39" s="18"/>
-      <c r="AY39" s="18"/>
-      <c r="AZ39" s="18"/>
-      <c r="BA39" s="18"/>
-      <c r="BB39" s="18"/>
-      <c r="BC39" s="19"/>
-      <c r="BD39" s="56" t="s">
+      <c r="AX39" s="47"/>
+      <c r="AY39" s="47"/>
+      <c r="AZ39" s="47"/>
+      <c r="BA39" s="47"/>
+      <c r="BB39" s="47"/>
+      <c r="BC39" s="48"/>
+      <c r="BD39" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="BE39" s="18"/>
-      <c r="BF39" s="18"/>
-      <c r="BG39" s="18"/>
-      <c r="BH39" s="18"/>
-      <c r="BI39" s="18"/>
-      <c r="BJ39" s="19"/>
+      <c r="BE39" s="47"/>
+      <c r="BF39" s="47"/>
+      <c r="BG39" s="47"/>
+      <c r="BH39" s="47"/>
+      <c r="BI39" s="47"/>
+      <c r="BJ39" s="48"/>
     </row>
     <row r="40" spans="1:78" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="13"/>
@@ -3513,54 +3553,54 @@
       <c r="L40" s="14"/>
       <c r="M40" s="14"/>
       <c r="N40" s="14"/>
-      <c r="O40" s="33"/>
-      <c r="P40" s="22"/>
-      <c r="Q40" s="22"/>
-      <c r="R40" s="22"/>
-      <c r="S40" s="22"/>
-      <c r="T40" s="22"/>
-      <c r="U40" s="23"/>
-      <c r="V40" s="20"/>
-      <c r="W40" s="22"/>
-      <c r="X40" s="22"/>
-      <c r="Y40" s="22"/>
-      <c r="Z40" s="22"/>
-      <c r="AA40" s="22"/>
-      <c r="AB40" s="23"/>
-      <c r="AC40" s="20"/>
-      <c r="AD40" s="22"/>
-      <c r="AE40" s="22"/>
-      <c r="AF40" s="22"/>
-      <c r="AG40" s="22"/>
-      <c r="AH40" s="22"/>
-      <c r="AI40" s="22"/>
-      <c r="AJ40" s="22"/>
-      <c r="AK40" s="22"/>
-      <c r="AL40" s="22"/>
-      <c r="AM40" s="22"/>
-      <c r="AN40" s="22"/>
-      <c r="AO40" s="23"/>
-      <c r="AP40" s="20"/>
-      <c r="AQ40" s="22"/>
-      <c r="AR40" s="22"/>
-      <c r="AS40" s="22"/>
-      <c r="AT40" s="22"/>
-      <c r="AU40" s="22"/>
-      <c r="AV40" s="23"/>
-      <c r="AW40" s="20"/>
-      <c r="AX40" s="21"/>
-      <c r="AY40" s="21"/>
-      <c r="AZ40" s="21"/>
-      <c r="BA40" s="21"/>
-      <c r="BB40" s="22"/>
-      <c r="BC40" s="23"/>
-      <c r="BD40" s="20"/>
-      <c r="BE40" s="22"/>
-      <c r="BF40" s="22"/>
-      <c r="BG40" s="22"/>
-      <c r="BH40" s="22"/>
-      <c r="BI40" s="22"/>
-      <c r="BJ40" s="23"/>
+      <c r="O40" s="69"/>
+      <c r="P40" s="56"/>
+      <c r="Q40" s="56"/>
+      <c r="R40" s="56"/>
+      <c r="S40" s="56"/>
+      <c r="T40" s="56"/>
+      <c r="U40" s="59"/>
+      <c r="V40" s="58"/>
+      <c r="W40" s="56"/>
+      <c r="X40" s="56"/>
+      <c r="Y40" s="56"/>
+      <c r="Z40" s="56"/>
+      <c r="AA40" s="56"/>
+      <c r="AB40" s="59"/>
+      <c r="AC40" s="58"/>
+      <c r="AD40" s="56"/>
+      <c r="AE40" s="56"/>
+      <c r="AF40" s="56"/>
+      <c r="AG40" s="56"/>
+      <c r="AH40" s="56"/>
+      <c r="AI40" s="56"/>
+      <c r="AJ40" s="56"/>
+      <c r="AK40" s="56"/>
+      <c r="AL40" s="56"/>
+      <c r="AM40" s="56"/>
+      <c r="AN40" s="56"/>
+      <c r="AO40" s="59"/>
+      <c r="AP40" s="58"/>
+      <c r="AQ40" s="56"/>
+      <c r="AR40" s="56"/>
+      <c r="AS40" s="56"/>
+      <c r="AT40" s="56"/>
+      <c r="AU40" s="56"/>
+      <c r="AV40" s="59"/>
+      <c r="AW40" s="58"/>
+      <c r="AX40" s="61"/>
+      <c r="AY40" s="61"/>
+      <c r="AZ40" s="61"/>
+      <c r="BA40" s="61"/>
+      <c r="BB40" s="56"/>
+      <c r="BC40" s="59"/>
+      <c r="BD40" s="58"/>
+      <c r="BE40" s="56"/>
+      <c r="BF40" s="56"/>
+      <c r="BG40" s="56"/>
+      <c r="BH40" s="56"/>
+      <c r="BI40" s="56"/>
+      <c r="BJ40" s="59"/>
     </row>
     <row r="41" spans="1:78" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="13"/>
@@ -3577,54 +3617,54 @@
       <c r="L41" s="14"/>
       <c r="M41" s="14"/>
       <c r="N41" s="14"/>
-      <c r="O41" s="34"/>
-      <c r="P41" s="25"/>
-      <c r="Q41" s="25"/>
-      <c r="R41" s="25"/>
-      <c r="S41" s="25"/>
-      <c r="T41" s="25"/>
-      <c r="U41" s="26"/>
-      <c r="V41" s="24"/>
-      <c r="W41" s="25"/>
-      <c r="X41" s="25"/>
-      <c r="Y41" s="25"/>
-      <c r="Z41" s="25"/>
-      <c r="AA41" s="25"/>
-      <c r="AB41" s="26"/>
-      <c r="AC41" s="24"/>
-      <c r="AD41" s="25"/>
-      <c r="AE41" s="25"/>
-      <c r="AF41" s="25"/>
-      <c r="AG41" s="25"/>
-      <c r="AH41" s="25"/>
-      <c r="AI41" s="25"/>
-      <c r="AJ41" s="25"/>
-      <c r="AK41" s="25"/>
-      <c r="AL41" s="25"/>
-      <c r="AM41" s="25"/>
-      <c r="AN41" s="25"/>
-      <c r="AO41" s="26"/>
-      <c r="AP41" s="24"/>
-      <c r="AQ41" s="25"/>
-      <c r="AR41" s="25"/>
-      <c r="AS41" s="25"/>
-      <c r="AT41" s="25"/>
-      <c r="AU41" s="25"/>
-      <c r="AV41" s="26"/>
-      <c r="AW41" s="24"/>
-      <c r="AX41" s="25"/>
-      <c r="AY41" s="25"/>
-      <c r="AZ41" s="25"/>
-      <c r="BA41" s="25"/>
-      <c r="BB41" s="25"/>
-      <c r="BC41" s="26"/>
-      <c r="BD41" s="24"/>
-      <c r="BE41" s="25"/>
-      <c r="BF41" s="25"/>
-      <c r="BG41" s="25"/>
-      <c r="BH41" s="25"/>
-      <c r="BI41" s="25"/>
-      <c r="BJ41" s="26"/>
+      <c r="O41" s="70"/>
+      <c r="P41" s="50"/>
+      <c r="Q41" s="50"/>
+      <c r="R41" s="50"/>
+      <c r="S41" s="50"/>
+      <c r="T41" s="50"/>
+      <c r="U41" s="51"/>
+      <c r="V41" s="49"/>
+      <c r="W41" s="50"/>
+      <c r="X41" s="50"/>
+      <c r="Y41" s="50"/>
+      <c r="Z41" s="50"/>
+      <c r="AA41" s="50"/>
+      <c r="AB41" s="51"/>
+      <c r="AC41" s="49"/>
+      <c r="AD41" s="50"/>
+      <c r="AE41" s="50"/>
+      <c r="AF41" s="50"/>
+      <c r="AG41" s="50"/>
+      <c r="AH41" s="50"/>
+      <c r="AI41" s="50"/>
+      <c r="AJ41" s="50"/>
+      <c r="AK41" s="50"/>
+      <c r="AL41" s="50"/>
+      <c r="AM41" s="50"/>
+      <c r="AN41" s="50"/>
+      <c r="AO41" s="51"/>
+      <c r="AP41" s="49"/>
+      <c r="AQ41" s="50"/>
+      <c r="AR41" s="50"/>
+      <c r="AS41" s="50"/>
+      <c r="AT41" s="50"/>
+      <c r="AU41" s="50"/>
+      <c r="AV41" s="51"/>
+      <c r="AW41" s="49"/>
+      <c r="AX41" s="50"/>
+      <c r="AY41" s="50"/>
+      <c r="AZ41" s="50"/>
+      <c r="BA41" s="50"/>
+      <c r="BB41" s="50"/>
+      <c r="BC41" s="51"/>
+      <c r="BD41" s="49"/>
+      <c r="BE41" s="50"/>
+      <c r="BF41" s="50"/>
+      <c r="BG41" s="50"/>
+      <c r="BH41" s="50"/>
+      <c r="BI41" s="50"/>
+      <c r="BJ41" s="51"/>
     </row>
     <row r="42" spans="1:78" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="13"/>
@@ -3641,69 +3681,69 @@
       <c r="L42" s="14"/>
       <c r="M42" s="14"/>
       <c r="N42" s="14"/>
-      <c r="O42" s="32" t="s">
+      <c r="O42" s="83" t="s">
         <v>6</v>
       </c>
-      <c r="P42" s="18"/>
-      <c r="Q42" s="18"/>
-      <c r="R42" s="18"/>
-      <c r="S42" s="18"/>
-      <c r="T42" s="18"/>
-      <c r="U42" s="19"/>
-      <c r="V42" s="49" t="s">
+      <c r="P42" s="47"/>
+      <c r="Q42" s="47"/>
+      <c r="R42" s="47"/>
+      <c r="S42" s="47"/>
+      <c r="T42" s="47"/>
+      <c r="U42" s="48"/>
+      <c r="V42" s="93" t="s">
         <v>12</v>
       </c>
-      <c r="W42" s="18"/>
-      <c r="X42" s="18"/>
-      <c r="Y42" s="18"/>
-      <c r="Z42" s="18"/>
-      <c r="AA42" s="18"/>
-      <c r="AB42" s="19"/>
-      <c r="AC42" s="63" t="s">
+      <c r="W42" s="47"/>
+      <c r="X42" s="47"/>
+      <c r="Y42" s="47"/>
+      <c r="Z42" s="47"/>
+      <c r="AA42" s="47"/>
+      <c r="AB42" s="48"/>
+      <c r="AC42" s="81" t="s">
         <v>29</v>
       </c>
-      <c r="AD42" s="18"/>
-      <c r="AE42" s="18"/>
-      <c r="AF42" s="18"/>
-      <c r="AG42" s="18"/>
-      <c r="AH42" s="18"/>
-      <c r="AI42" s="18"/>
-      <c r="AJ42" s="18"/>
-      <c r="AK42" s="18"/>
-      <c r="AL42" s="18"/>
-      <c r="AM42" s="18"/>
-      <c r="AN42" s="18"/>
-      <c r="AO42" s="19"/>
-      <c r="AP42" s="17" t="str">
+      <c r="AD42" s="47"/>
+      <c r="AE42" s="47"/>
+      <c r="AF42" s="47"/>
+      <c r="AG42" s="47"/>
+      <c r="AH42" s="47"/>
+      <c r="AI42" s="47"/>
+      <c r="AJ42" s="47"/>
+      <c r="AK42" s="47"/>
+      <c r="AL42" s="47"/>
+      <c r="AM42" s="47"/>
+      <c r="AN42" s="47"/>
+      <c r="AO42" s="48"/>
+      <c r="AP42" s="92" t="str">
         <f>BO3</f>
         <v>JULIO 23 DEL 2026</v>
       </c>
-      <c r="AQ42" s="18"/>
-      <c r="AR42" s="18"/>
-      <c r="AS42" s="18"/>
-      <c r="AT42" s="18"/>
-      <c r="AU42" s="18"/>
-      <c r="AV42" s="19"/>
-      <c r="AW42" s="17" t="str">
+      <c r="AQ42" s="47"/>
+      <c r="AR42" s="47"/>
+      <c r="AS42" s="47"/>
+      <c r="AT42" s="47"/>
+      <c r="AU42" s="47"/>
+      <c r="AV42" s="48"/>
+      <c r="AW42" s="92" t="str">
         <f>AT27</f>
         <v>Fecha :JULIO 24 DEL 2026</v>
       </c>
-      <c r="AX42" s="18"/>
-      <c r="AY42" s="18"/>
-      <c r="AZ42" s="18"/>
-      <c r="BA42" s="18"/>
-      <c r="BB42" s="18"/>
-      <c r="BC42" s="19"/>
-      <c r="BD42" s="62" t="str">
+      <c r="AX42" s="47"/>
+      <c r="AY42" s="47"/>
+      <c r="AZ42" s="47"/>
+      <c r="BA42" s="47"/>
+      <c r="BB42" s="47"/>
+      <c r="BC42" s="48"/>
+      <c r="BD42" s="80" t="str">
         <f>BO5</f>
         <v>F.NAVIA</v>
       </c>
-      <c r="BE42" s="18"/>
-      <c r="BF42" s="18"/>
-      <c r="BG42" s="18"/>
-      <c r="BH42" s="18"/>
-      <c r="BI42" s="18"/>
-      <c r="BJ42" s="19"/>
+      <c r="BE42" s="47"/>
+      <c r="BF42" s="47"/>
+      <c r="BG42" s="47"/>
+      <c r="BH42" s="47"/>
+      <c r="BI42" s="47"/>
+      <c r="BJ42" s="48"/>
     </row>
     <row r="43" spans="1:78" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="13"/>
@@ -3720,61 +3760,61 @@
       <c r="L43" s="14"/>
       <c r="M43" s="14"/>
       <c r="N43" s="14"/>
-      <c r="O43" s="33"/>
-      <c r="P43" s="22"/>
-      <c r="Q43" s="22"/>
-      <c r="R43" s="22"/>
-      <c r="S43" s="22"/>
-      <c r="T43" s="22"/>
-      <c r="U43" s="23"/>
-      <c r="V43" s="20"/>
-      <c r="W43" s="22"/>
-      <c r="X43" s="22"/>
-      <c r="Y43" s="22"/>
-      <c r="Z43" s="22"/>
-      <c r="AA43" s="22"/>
-      <c r="AB43" s="23"/>
-      <c r="AC43" s="20"/>
-      <c r="AD43" s="22"/>
-      <c r="AE43" s="22"/>
-      <c r="AF43" s="22"/>
-      <c r="AG43" s="22"/>
-      <c r="AH43" s="22"/>
-      <c r="AI43" s="22"/>
-      <c r="AJ43" s="22"/>
-      <c r="AK43" s="22"/>
-      <c r="AL43" s="22"/>
-      <c r="AM43" s="22"/>
-      <c r="AN43" s="22"/>
-      <c r="AO43" s="23"/>
-      <c r="AP43" s="20"/>
-      <c r="AQ43" s="22"/>
-      <c r="AR43" s="22"/>
-      <c r="AS43" s="22"/>
-      <c r="AT43" s="22"/>
-      <c r="AU43" s="22"/>
-      <c r="AV43" s="23"/>
-      <c r="AW43" s="20"/>
-      <c r="AX43" s="21"/>
-      <c r="AY43" s="21"/>
-      <c r="AZ43" s="21"/>
-      <c r="BA43" s="21"/>
-      <c r="BB43" s="22"/>
-      <c r="BC43" s="23"/>
-      <c r="BD43" s="20"/>
-      <c r="BE43" s="22"/>
-      <c r="BF43" s="22"/>
-      <c r="BG43" s="22"/>
-      <c r="BH43" s="22"/>
-      <c r="BI43" s="22"/>
-      <c r="BJ43" s="23"/>
-      <c r="BP43" s="48"/>
-      <c r="BQ43" s="22"/>
-      <c r="BR43" s="22"/>
-      <c r="BS43" s="22"/>
-      <c r="BT43" s="22"/>
-      <c r="BU43" s="22"/>
-      <c r="BV43" s="22"/>
+      <c r="O43" s="69"/>
+      <c r="P43" s="56"/>
+      <c r="Q43" s="56"/>
+      <c r="R43" s="56"/>
+      <c r="S43" s="56"/>
+      <c r="T43" s="56"/>
+      <c r="U43" s="59"/>
+      <c r="V43" s="58"/>
+      <c r="W43" s="56"/>
+      <c r="X43" s="56"/>
+      <c r="Y43" s="56"/>
+      <c r="Z43" s="56"/>
+      <c r="AA43" s="56"/>
+      <c r="AB43" s="59"/>
+      <c r="AC43" s="58"/>
+      <c r="AD43" s="56"/>
+      <c r="AE43" s="56"/>
+      <c r="AF43" s="56"/>
+      <c r="AG43" s="56"/>
+      <c r="AH43" s="56"/>
+      <c r="AI43" s="56"/>
+      <c r="AJ43" s="56"/>
+      <c r="AK43" s="56"/>
+      <c r="AL43" s="56"/>
+      <c r="AM43" s="56"/>
+      <c r="AN43" s="56"/>
+      <c r="AO43" s="59"/>
+      <c r="AP43" s="58"/>
+      <c r="AQ43" s="56"/>
+      <c r="AR43" s="56"/>
+      <c r="AS43" s="56"/>
+      <c r="AT43" s="56"/>
+      <c r="AU43" s="56"/>
+      <c r="AV43" s="59"/>
+      <c r="AW43" s="58"/>
+      <c r="AX43" s="61"/>
+      <c r="AY43" s="61"/>
+      <c r="AZ43" s="61"/>
+      <c r="BA43" s="61"/>
+      <c r="BB43" s="56"/>
+      <c r="BC43" s="59"/>
+      <c r="BD43" s="58"/>
+      <c r="BE43" s="56"/>
+      <c r="BF43" s="56"/>
+      <c r="BG43" s="56"/>
+      <c r="BH43" s="56"/>
+      <c r="BI43" s="56"/>
+      <c r="BJ43" s="59"/>
+      <c r="BP43" s="91"/>
+      <c r="BQ43" s="56"/>
+      <c r="BR43" s="56"/>
+      <c r="BS43" s="56"/>
+      <c r="BT43" s="56"/>
+      <c r="BU43" s="56"/>
+      <c r="BV43" s="56"/>
     </row>
     <row r="44" spans="1:78" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="13"/>
@@ -3791,54 +3831,54 @@
       <c r="L44" s="14"/>
       <c r="M44" s="14"/>
       <c r="N44" s="14"/>
-      <c r="O44" s="34"/>
-      <c r="P44" s="25"/>
-      <c r="Q44" s="25"/>
-      <c r="R44" s="25"/>
-      <c r="S44" s="25"/>
-      <c r="T44" s="25"/>
-      <c r="U44" s="26"/>
-      <c r="V44" s="24"/>
-      <c r="W44" s="25"/>
-      <c r="X44" s="25"/>
-      <c r="Y44" s="25"/>
-      <c r="Z44" s="25"/>
-      <c r="AA44" s="25"/>
-      <c r="AB44" s="26"/>
-      <c r="AC44" s="24"/>
-      <c r="AD44" s="25"/>
-      <c r="AE44" s="25"/>
-      <c r="AF44" s="25"/>
-      <c r="AG44" s="25"/>
-      <c r="AH44" s="25"/>
-      <c r="AI44" s="25"/>
-      <c r="AJ44" s="25"/>
-      <c r="AK44" s="25"/>
-      <c r="AL44" s="25"/>
-      <c r="AM44" s="25"/>
-      <c r="AN44" s="25"/>
-      <c r="AO44" s="26"/>
-      <c r="AP44" s="24"/>
-      <c r="AQ44" s="25"/>
-      <c r="AR44" s="25"/>
-      <c r="AS44" s="25"/>
-      <c r="AT44" s="25"/>
-      <c r="AU44" s="25"/>
-      <c r="AV44" s="26"/>
-      <c r="AW44" s="24"/>
-      <c r="AX44" s="25"/>
-      <c r="AY44" s="25"/>
-      <c r="AZ44" s="25"/>
-      <c r="BA44" s="25"/>
-      <c r="BB44" s="25"/>
-      <c r="BC44" s="26"/>
-      <c r="BD44" s="24"/>
-      <c r="BE44" s="25"/>
-      <c r="BF44" s="25"/>
-      <c r="BG44" s="25"/>
-      <c r="BH44" s="25"/>
-      <c r="BI44" s="25"/>
-      <c r="BJ44" s="26"/>
+      <c r="O44" s="70"/>
+      <c r="P44" s="50"/>
+      <c r="Q44" s="50"/>
+      <c r="R44" s="50"/>
+      <c r="S44" s="50"/>
+      <c r="T44" s="50"/>
+      <c r="U44" s="51"/>
+      <c r="V44" s="49"/>
+      <c r="W44" s="50"/>
+      <c r="X44" s="50"/>
+      <c r="Y44" s="50"/>
+      <c r="Z44" s="50"/>
+      <c r="AA44" s="50"/>
+      <c r="AB44" s="51"/>
+      <c r="AC44" s="49"/>
+      <c r="AD44" s="50"/>
+      <c r="AE44" s="50"/>
+      <c r="AF44" s="50"/>
+      <c r="AG44" s="50"/>
+      <c r="AH44" s="50"/>
+      <c r="AI44" s="50"/>
+      <c r="AJ44" s="50"/>
+      <c r="AK44" s="50"/>
+      <c r="AL44" s="50"/>
+      <c r="AM44" s="50"/>
+      <c r="AN44" s="50"/>
+      <c r="AO44" s="51"/>
+      <c r="AP44" s="49"/>
+      <c r="AQ44" s="50"/>
+      <c r="AR44" s="50"/>
+      <c r="AS44" s="50"/>
+      <c r="AT44" s="50"/>
+      <c r="AU44" s="50"/>
+      <c r="AV44" s="51"/>
+      <c r="AW44" s="49"/>
+      <c r="AX44" s="50"/>
+      <c r="AY44" s="50"/>
+      <c r="AZ44" s="50"/>
+      <c r="BA44" s="50"/>
+      <c r="BB44" s="50"/>
+      <c r="BC44" s="51"/>
+      <c r="BD44" s="49"/>
+      <c r="BE44" s="50"/>
+      <c r="BF44" s="50"/>
+      <c r="BG44" s="50"/>
+      <c r="BH44" s="50"/>
+      <c r="BI44" s="50"/>
+      <c r="BJ44" s="51"/>
     </row>
     <row r="45" spans="1:78" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="13"/>
@@ -3855,54 +3895,54 @@
       <c r="L45" s="14"/>
       <c r="M45" s="14"/>
       <c r="N45" s="14"/>
-      <c r="O45" s="57"/>
-      <c r="P45" s="18"/>
-      <c r="Q45" s="18"/>
-      <c r="R45" s="18"/>
-      <c r="S45" s="18"/>
-      <c r="T45" s="18"/>
-      <c r="U45" s="19"/>
-      <c r="V45" s="27"/>
-      <c r="W45" s="18"/>
-      <c r="X45" s="18"/>
-      <c r="Y45" s="18"/>
-      <c r="Z45" s="18"/>
-      <c r="AA45" s="18"/>
-      <c r="AB45" s="19"/>
-      <c r="AC45" s="39"/>
-      <c r="AD45" s="18"/>
-      <c r="AE45" s="18"/>
-      <c r="AF45" s="18"/>
-      <c r="AG45" s="18"/>
-      <c r="AH45" s="18"/>
-      <c r="AI45" s="18"/>
-      <c r="AJ45" s="18"/>
-      <c r="AK45" s="18"/>
-      <c r="AL45" s="18"/>
-      <c r="AM45" s="18"/>
-      <c r="AN45" s="18"/>
-      <c r="AO45" s="19"/>
-      <c r="AP45" s="27"/>
-      <c r="AQ45" s="18"/>
-      <c r="AR45" s="18"/>
-      <c r="AS45" s="18"/>
-      <c r="AT45" s="18"/>
-      <c r="AU45" s="18"/>
-      <c r="AV45" s="19"/>
-      <c r="AW45" s="27"/>
-      <c r="AX45" s="18"/>
-      <c r="AY45" s="18"/>
-      <c r="AZ45" s="18"/>
-      <c r="BA45" s="18"/>
-      <c r="BB45" s="18"/>
-      <c r="BC45" s="19"/>
-      <c r="BD45" s="27"/>
-      <c r="BE45" s="18"/>
-      <c r="BF45" s="18"/>
-      <c r="BG45" s="18"/>
-      <c r="BH45" s="18"/>
-      <c r="BI45" s="18"/>
-      <c r="BJ45" s="19"/>
+      <c r="O45" s="72"/>
+      <c r="P45" s="47"/>
+      <c r="Q45" s="47"/>
+      <c r="R45" s="47"/>
+      <c r="S45" s="47"/>
+      <c r="T45" s="47"/>
+      <c r="U45" s="48"/>
+      <c r="V45" s="84"/>
+      <c r="W45" s="47"/>
+      <c r="X45" s="47"/>
+      <c r="Y45" s="47"/>
+      <c r="Z45" s="47"/>
+      <c r="AA45" s="47"/>
+      <c r="AB45" s="48"/>
+      <c r="AC45" s="85"/>
+      <c r="AD45" s="47"/>
+      <c r="AE45" s="47"/>
+      <c r="AF45" s="47"/>
+      <c r="AG45" s="47"/>
+      <c r="AH45" s="47"/>
+      <c r="AI45" s="47"/>
+      <c r="AJ45" s="47"/>
+      <c r="AK45" s="47"/>
+      <c r="AL45" s="47"/>
+      <c r="AM45" s="47"/>
+      <c r="AN45" s="47"/>
+      <c r="AO45" s="48"/>
+      <c r="AP45" s="84"/>
+      <c r="AQ45" s="47"/>
+      <c r="AR45" s="47"/>
+      <c r="AS45" s="47"/>
+      <c r="AT45" s="47"/>
+      <c r="AU45" s="47"/>
+      <c r="AV45" s="48"/>
+      <c r="AW45" s="84"/>
+      <c r="AX45" s="47"/>
+      <c r="AY45" s="47"/>
+      <c r="AZ45" s="47"/>
+      <c r="BA45" s="47"/>
+      <c r="BB45" s="47"/>
+      <c r="BC45" s="48"/>
+      <c r="BD45" s="84"/>
+      <c r="BE45" s="47"/>
+      <c r="BF45" s="47"/>
+      <c r="BG45" s="47"/>
+      <c r="BH45" s="47"/>
+      <c r="BI45" s="47"/>
+      <c r="BJ45" s="48"/>
     </row>
     <row r="46" spans="1:78" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="13"/>
@@ -3919,54 +3959,54 @@
       <c r="L46" s="14"/>
       <c r="M46" s="14"/>
       <c r="N46" s="14"/>
-      <c r="O46" s="33"/>
-      <c r="P46" s="22"/>
-      <c r="Q46" s="22"/>
-      <c r="R46" s="22"/>
-      <c r="S46" s="22"/>
-      <c r="T46" s="22"/>
-      <c r="U46" s="23"/>
-      <c r="V46" s="20"/>
-      <c r="W46" s="22"/>
-      <c r="X46" s="22"/>
-      <c r="Y46" s="22"/>
-      <c r="Z46" s="22"/>
-      <c r="AA46" s="22"/>
-      <c r="AB46" s="23"/>
-      <c r="AC46" s="20"/>
-      <c r="AD46" s="22"/>
-      <c r="AE46" s="22"/>
-      <c r="AF46" s="22"/>
-      <c r="AG46" s="22"/>
-      <c r="AH46" s="22"/>
-      <c r="AI46" s="22"/>
-      <c r="AJ46" s="22"/>
-      <c r="AK46" s="22"/>
-      <c r="AL46" s="22"/>
-      <c r="AM46" s="22"/>
-      <c r="AN46" s="22"/>
-      <c r="AO46" s="23"/>
-      <c r="AP46" s="20"/>
-      <c r="AQ46" s="22"/>
-      <c r="AR46" s="22"/>
-      <c r="AS46" s="22"/>
-      <c r="AT46" s="22"/>
-      <c r="AU46" s="22"/>
-      <c r="AV46" s="23"/>
-      <c r="AW46" s="20"/>
-      <c r="AX46" s="21"/>
-      <c r="AY46" s="21"/>
-      <c r="AZ46" s="21"/>
-      <c r="BA46" s="21"/>
-      <c r="BB46" s="22"/>
-      <c r="BC46" s="23"/>
-      <c r="BD46" s="20"/>
-      <c r="BE46" s="22"/>
-      <c r="BF46" s="22"/>
-      <c r="BG46" s="22"/>
-      <c r="BH46" s="22"/>
-      <c r="BI46" s="22"/>
-      <c r="BJ46" s="23"/>
+      <c r="O46" s="69"/>
+      <c r="P46" s="56"/>
+      <c r="Q46" s="56"/>
+      <c r="R46" s="56"/>
+      <c r="S46" s="56"/>
+      <c r="T46" s="56"/>
+      <c r="U46" s="59"/>
+      <c r="V46" s="58"/>
+      <c r="W46" s="56"/>
+      <c r="X46" s="56"/>
+      <c r="Y46" s="56"/>
+      <c r="Z46" s="56"/>
+      <c r="AA46" s="56"/>
+      <c r="AB46" s="59"/>
+      <c r="AC46" s="58"/>
+      <c r="AD46" s="56"/>
+      <c r="AE46" s="56"/>
+      <c r="AF46" s="56"/>
+      <c r="AG46" s="56"/>
+      <c r="AH46" s="56"/>
+      <c r="AI46" s="56"/>
+      <c r="AJ46" s="56"/>
+      <c r="AK46" s="56"/>
+      <c r="AL46" s="56"/>
+      <c r="AM46" s="56"/>
+      <c r="AN46" s="56"/>
+      <c r="AO46" s="59"/>
+      <c r="AP46" s="58"/>
+      <c r="AQ46" s="56"/>
+      <c r="AR46" s="56"/>
+      <c r="AS46" s="56"/>
+      <c r="AT46" s="56"/>
+      <c r="AU46" s="56"/>
+      <c r="AV46" s="59"/>
+      <c r="AW46" s="58"/>
+      <c r="AX46" s="61"/>
+      <c r="AY46" s="61"/>
+      <c r="AZ46" s="61"/>
+      <c r="BA46" s="61"/>
+      <c r="BB46" s="56"/>
+      <c r="BC46" s="59"/>
+      <c r="BD46" s="58"/>
+      <c r="BE46" s="56"/>
+      <c r="BF46" s="56"/>
+      <c r="BG46" s="56"/>
+      <c r="BH46" s="56"/>
+      <c r="BI46" s="56"/>
+      <c r="BJ46" s="59"/>
     </row>
     <row r="47" spans="1:78" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="13"/>
@@ -3983,54 +4023,54 @@
       <c r="L47" s="14"/>
       <c r="M47" s="14"/>
       <c r="N47" s="14"/>
-      <c r="O47" s="34"/>
-      <c r="P47" s="25"/>
-      <c r="Q47" s="25"/>
-      <c r="R47" s="25"/>
-      <c r="S47" s="25"/>
-      <c r="T47" s="25"/>
-      <c r="U47" s="26"/>
-      <c r="V47" s="24"/>
-      <c r="W47" s="25"/>
-      <c r="X47" s="25"/>
-      <c r="Y47" s="25"/>
-      <c r="Z47" s="25"/>
-      <c r="AA47" s="25"/>
-      <c r="AB47" s="26"/>
-      <c r="AC47" s="24"/>
-      <c r="AD47" s="25"/>
-      <c r="AE47" s="25"/>
-      <c r="AF47" s="25"/>
-      <c r="AG47" s="25"/>
-      <c r="AH47" s="25"/>
-      <c r="AI47" s="25"/>
-      <c r="AJ47" s="25"/>
-      <c r="AK47" s="25"/>
-      <c r="AL47" s="25"/>
-      <c r="AM47" s="25"/>
-      <c r="AN47" s="25"/>
-      <c r="AO47" s="26"/>
-      <c r="AP47" s="24"/>
-      <c r="AQ47" s="25"/>
-      <c r="AR47" s="25"/>
-      <c r="AS47" s="25"/>
-      <c r="AT47" s="25"/>
-      <c r="AU47" s="25"/>
-      <c r="AV47" s="26"/>
-      <c r="AW47" s="24"/>
-      <c r="AX47" s="25"/>
-      <c r="AY47" s="25"/>
-      <c r="AZ47" s="25"/>
-      <c r="BA47" s="25"/>
-      <c r="BB47" s="25"/>
-      <c r="BC47" s="26"/>
-      <c r="BD47" s="24"/>
-      <c r="BE47" s="25"/>
-      <c r="BF47" s="25"/>
-      <c r="BG47" s="25"/>
-      <c r="BH47" s="25"/>
-      <c r="BI47" s="25"/>
-      <c r="BJ47" s="26"/>
+      <c r="O47" s="70"/>
+      <c r="P47" s="50"/>
+      <c r="Q47" s="50"/>
+      <c r="R47" s="50"/>
+      <c r="S47" s="50"/>
+      <c r="T47" s="50"/>
+      <c r="U47" s="51"/>
+      <c r="V47" s="49"/>
+      <c r="W47" s="50"/>
+      <c r="X47" s="50"/>
+      <c r="Y47" s="50"/>
+      <c r="Z47" s="50"/>
+      <c r="AA47" s="50"/>
+      <c r="AB47" s="51"/>
+      <c r="AC47" s="49"/>
+      <c r="AD47" s="50"/>
+      <c r="AE47" s="50"/>
+      <c r="AF47" s="50"/>
+      <c r="AG47" s="50"/>
+      <c r="AH47" s="50"/>
+      <c r="AI47" s="50"/>
+      <c r="AJ47" s="50"/>
+      <c r="AK47" s="50"/>
+      <c r="AL47" s="50"/>
+      <c r="AM47" s="50"/>
+      <c r="AN47" s="50"/>
+      <c r="AO47" s="51"/>
+      <c r="AP47" s="49"/>
+      <c r="AQ47" s="50"/>
+      <c r="AR47" s="50"/>
+      <c r="AS47" s="50"/>
+      <c r="AT47" s="50"/>
+      <c r="AU47" s="50"/>
+      <c r="AV47" s="51"/>
+      <c r="AW47" s="49"/>
+      <c r="AX47" s="50"/>
+      <c r="AY47" s="50"/>
+      <c r="AZ47" s="50"/>
+      <c r="BA47" s="50"/>
+      <c r="BB47" s="50"/>
+      <c r="BC47" s="51"/>
+      <c r="BD47" s="49"/>
+      <c r="BE47" s="50"/>
+      <c r="BF47" s="50"/>
+      <c r="BG47" s="50"/>
+      <c r="BH47" s="50"/>
+      <c r="BI47" s="50"/>
+      <c r="BJ47" s="51"/>
     </row>
     <row r="48" spans="1:78" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="13"/>
@@ -4047,54 +4087,54 @@
       <c r="L48" s="13"/>
       <c r="M48" s="13"/>
       <c r="N48" s="13"/>
-      <c r="O48" s="40"/>
-      <c r="P48" s="22"/>
-      <c r="Q48" s="22"/>
-      <c r="R48" s="22"/>
-      <c r="S48" s="22"/>
-      <c r="T48" s="22"/>
-      <c r="U48" s="22"/>
-      <c r="V48" s="31"/>
-      <c r="W48" s="22"/>
-      <c r="X48" s="22"/>
-      <c r="Y48" s="22"/>
-      <c r="Z48" s="22"/>
-      <c r="AA48" s="22"/>
-      <c r="AB48" s="22"/>
-      <c r="AC48" s="31"/>
-      <c r="AD48" s="22"/>
-      <c r="AE48" s="22"/>
-      <c r="AF48" s="22"/>
-      <c r="AG48" s="22"/>
-      <c r="AH48" s="22"/>
-      <c r="AI48" s="22"/>
-      <c r="AJ48" s="22"/>
-      <c r="AK48" s="22"/>
-      <c r="AL48" s="22"/>
-      <c r="AM48" s="22"/>
-      <c r="AN48" s="22"/>
-      <c r="AO48" s="22"/>
-      <c r="AP48" s="31"/>
-      <c r="AQ48" s="22"/>
-      <c r="AR48" s="22"/>
-      <c r="AS48" s="22"/>
-      <c r="AT48" s="22"/>
-      <c r="AU48" s="22"/>
-      <c r="AV48" s="22"/>
-      <c r="AW48" s="31"/>
-      <c r="AX48" s="21"/>
-      <c r="AY48" s="21"/>
-      <c r="AZ48" s="21"/>
-      <c r="BA48" s="21"/>
-      <c r="BB48" s="22"/>
-      <c r="BC48" s="22"/>
-      <c r="BD48" s="31"/>
-      <c r="BE48" s="22"/>
-      <c r="BF48" s="22"/>
-      <c r="BG48" s="22"/>
-      <c r="BH48" s="22"/>
-      <c r="BI48" s="22"/>
-      <c r="BJ48" s="22"/>
+      <c r="O48" s="86"/>
+      <c r="P48" s="56"/>
+      <c r="Q48" s="56"/>
+      <c r="R48" s="56"/>
+      <c r="S48" s="56"/>
+      <c r="T48" s="56"/>
+      <c r="U48" s="56"/>
+      <c r="V48" s="55"/>
+      <c r="W48" s="56"/>
+      <c r="X48" s="56"/>
+      <c r="Y48" s="56"/>
+      <c r="Z48" s="56"/>
+      <c r="AA48" s="56"/>
+      <c r="AB48" s="56"/>
+      <c r="AC48" s="55"/>
+      <c r="AD48" s="56"/>
+      <c r="AE48" s="56"/>
+      <c r="AF48" s="56"/>
+      <c r="AG48" s="56"/>
+      <c r="AH48" s="56"/>
+      <c r="AI48" s="56"/>
+      <c r="AJ48" s="56"/>
+      <c r="AK48" s="56"/>
+      <c r="AL48" s="56"/>
+      <c r="AM48" s="56"/>
+      <c r="AN48" s="56"/>
+      <c r="AO48" s="56"/>
+      <c r="AP48" s="55"/>
+      <c r="AQ48" s="56"/>
+      <c r="AR48" s="56"/>
+      <c r="AS48" s="56"/>
+      <c r="AT48" s="56"/>
+      <c r="AU48" s="56"/>
+      <c r="AV48" s="56"/>
+      <c r="AW48" s="55"/>
+      <c r="AX48" s="61"/>
+      <c r="AY48" s="61"/>
+      <c r="AZ48" s="61"/>
+      <c r="BA48" s="61"/>
+      <c r="BB48" s="56"/>
+      <c r="BC48" s="56"/>
+      <c r="BD48" s="55"/>
+      <c r="BE48" s="56"/>
+      <c r="BF48" s="56"/>
+      <c r="BG48" s="56"/>
+      <c r="BH48" s="56"/>
+      <c r="BI48" s="56"/>
+      <c r="BJ48" s="56"/>
     </row>
     <row r="49" spans="1:70" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="13"/>
@@ -4111,54 +4151,54 @@
       <c r="L49" s="13"/>
       <c r="M49" s="13"/>
       <c r="N49" s="13"/>
-      <c r="O49" s="41"/>
-      <c r="P49" s="22"/>
-      <c r="Q49" s="22"/>
-      <c r="R49" s="22"/>
-      <c r="S49" s="22"/>
-      <c r="T49" s="22"/>
-      <c r="U49" s="22"/>
-      <c r="V49" s="22"/>
-      <c r="W49" s="22"/>
-      <c r="X49" s="22"/>
-      <c r="Y49" s="22"/>
-      <c r="Z49" s="22"/>
-      <c r="AA49" s="22"/>
-      <c r="AB49" s="22"/>
-      <c r="AC49" s="22"/>
-      <c r="AD49" s="22"/>
-      <c r="AE49" s="22"/>
-      <c r="AF49" s="22"/>
-      <c r="AG49" s="22"/>
-      <c r="AH49" s="22"/>
-      <c r="AI49" s="22"/>
-      <c r="AJ49" s="22"/>
-      <c r="AK49" s="22"/>
-      <c r="AL49" s="22"/>
-      <c r="AM49" s="22"/>
-      <c r="AN49" s="22"/>
-      <c r="AO49" s="22"/>
-      <c r="AP49" s="22"/>
-      <c r="AQ49" s="22"/>
-      <c r="AR49" s="22"/>
-      <c r="AS49" s="22"/>
-      <c r="AT49" s="22"/>
-      <c r="AU49" s="22"/>
-      <c r="AV49" s="22"/>
-      <c r="AW49" s="21"/>
-      <c r="AX49" s="21"/>
-      <c r="AY49" s="21"/>
-      <c r="AZ49" s="21"/>
-      <c r="BA49" s="21"/>
-      <c r="BB49" s="22"/>
-      <c r="BC49" s="22"/>
-      <c r="BD49" s="22"/>
-      <c r="BE49" s="22"/>
-      <c r="BF49" s="22"/>
-      <c r="BG49" s="22"/>
-      <c r="BH49" s="22"/>
-      <c r="BI49" s="22"/>
-      <c r="BJ49" s="22"/>
+      <c r="O49" s="76"/>
+      <c r="P49" s="56"/>
+      <c r="Q49" s="56"/>
+      <c r="R49" s="56"/>
+      <c r="S49" s="56"/>
+      <c r="T49" s="56"/>
+      <c r="U49" s="56"/>
+      <c r="V49" s="56"/>
+      <c r="W49" s="56"/>
+      <c r="X49" s="56"/>
+      <c r="Y49" s="56"/>
+      <c r="Z49" s="56"/>
+      <c r="AA49" s="56"/>
+      <c r="AB49" s="56"/>
+      <c r="AC49" s="56"/>
+      <c r="AD49" s="56"/>
+      <c r="AE49" s="56"/>
+      <c r="AF49" s="56"/>
+      <c r="AG49" s="56"/>
+      <c r="AH49" s="56"/>
+      <c r="AI49" s="56"/>
+      <c r="AJ49" s="56"/>
+      <c r="AK49" s="56"/>
+      <c r="AL49" s="56"/>
+      <c r="AM49" s="56"/>
+      <c r="AN49" s="56"/>
+      <c r="AO49" s="56"/>
+      <c r="AP49" s="56"/>
+      <c r="AQ49" s="56"/>
+      <c r="AR49" s="56"/>
+      <c r="AS49" s="56"/>
+      <c r="AT49" s="56"/>
+      <c r="AU49" s="56"/>
+      <c r="AV49" s="56"/>
+      <c r="AW49" s="61"/>
+      <c r="AX49" s="61"/>
+      <c r="AY49" s="61"/>
+      <c r="AZ49" s="61"/>
+      <c r="BA49" s="61"/>
+      <c r="BB49" s="56"/>
+      <c r="BC49" s="56"/>
+      <c r="BD49" s="56"/>
+      <c r="BE49" s="56"/>
+      <c r="BF49" s="56"/>
+      <c r="BG49" s="56"/>
+      <c r="BH49" s="56"/>
+      <c r="BI49" s="56"/>
+      <c r="BJ49" s="56"/>
     </row>
     <row r="50" spans="1:70" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="13"/>
@@ -4175,54 +4215,54 @@
       <c r="L50" s="13"/>
       <c r="M50" s="13"/>
       <c r="N50" s="13"/>
-      <c r="O50" s="41"/>
-      <c r="P50" s="22"/>
-      <c r="Q50" s="22"/>
-      <c r="R50" s="22"/>
-      <c r="S50" s="22"/>
-      <c r="T50" s="22"/>
-      <c r="U50" s="22"/>
-      <c r="V50" s="22"/>
-      <c r="W50" s="22"/>
-      <c r="X50" s="22"/>
-      <c r="Y50" s="22"/>
-      <c r="Z50" s="22"/>
-      <c r="AA50" s="22"/>
-      <c r="AB50" s="22"/>
-      <c r="AC50" s="22"/>
-      <c r="AD50" s="22"/>
-      <c r="AE50" s="22"/>
-      <c r="AF50" s="22"/>
-      <c r="AG50" s="22"/>
-      <c r="AH50" s="22"/>
-      <c r="AI50" s="22"/>
-      <c r="AJ50" s="22"/>
-      <c r="AK50" s="22"/>
-      <c r="AL50" s="22"/>
-      <c r="AM50" s="22"/>
-      <c r="AN50" s="22"/>
-      <c r="AO50" s="22"/>
-      <c r="AP50" s="22"/>
-      <c r="AQ50" s="22"/>
-      <c r="AR50" s="22"/>
-      <c r="AS50" s="22"/>
-      <c r="AT50" s="22"/>
-      <c r="AU50" s="22"/>
-      <c r="AV50" s="22"/>
-      <c r="AW50" s="21"/>
-      <c r="AX50" s="21"/>
-      <c r="AY50" s="21"/>
-      <c r="AZ50" s="21"/>
-      <c r="BA50" s="21"/>
-      <c r="BB50" s="22"/>
-      <c r="BC50" s="22"/>
-      <c r="BD50" s="22"/>
-      <c r="BE50" s="22"/>
-      <c r="BF50" s="22"/>
-      <c r="BG50" s="22"/>
-      <c r="BH50" s="22"/>
-      <c r="BI50" s="22"/>
-      <c r="BJ50" s="22"/>
+      <c r="O50" s="76"/>
+      <c r="P50" s="56"/>
+      <c r="Q50" s="56"/>
+      <c r="R50" s="56"/>
+      <c r="S50" s="56"/>
+      <c r="T50" s="56"/>
+      <c r="U50" s="56"/>
+      <c r="V50" s="56"/>
+      <c r="W50" s="56"/>
+      <c r="X50" s="56"/>
+      <c r="Y50" s="56"/>
+      <c r="Z50" s="56"/>
+      <c r="AA50" s="56"/>
+      <c r="AB50" s="56"/>
+      <c r="AC50" s="56"/>
+      <c r="AD50" s="56"/>
+      <c r="AE50" s="56"/>
+      <c r="AF50" s="56"/>
+      <c r="AG50" s="56"/>
+      <c r="AH50" s="56"/>
+      <c r="AI50" s="56"/>
+      <c r="AJ50" s="56"/>
+      <c r="AK50" s="56"/>
+      <c r="AL50" s="56"/>
+      <c r="AM50" s="56"/>
+      <c r="AN50" s="56"/>
+      <c r="AO50" s="56"/>
+      <c r="AP50" s="56"/>
+      <c r="AQ50" s="56"/>
+      <c r="AR50" s="56"/>
+      <c r="AS50" s="56"/>
+      <c r="AT50" s="56"/>
+      <c r="AU50" s="56"/>
+      <c r="AV50" s="56"/>
+      <c r="AW50" s="61"/>
+      <c r="AX50" s="61"/>
+      <c r="AY50" s="61"/>
+      <c r="AZ50" s="61"/>
+      <c r="BA50" s="61"/>
+      <c r="BB50" s="56"/>
+      <c r="BC50" s="56"/>
+      <c r="BD50" s="56"/>
+      <c r="BE50" s="56"/>
+      <c r="BF50" s="56"/>
+      <c r="BG50" s="56"/>
+      <c r="BH50" s="56"/>
+      <c r="BI50" s="56"/>
+      <c r="BJ50" s="56"/>
     </row>
     <row r="51" spans="1:70" ht="15" x14ac:dyDescent="0.35">
       <c r="A51" s="13"/>
@@ -4328,12 +4368,37 @@
     </row>
   </sheetData>
   <mergeCells count="54">
-    <mergeCell ref="Z3:BB4"/>
-    <mergeCell ref="BO6:BZ6"/>
-    <mergeCell ref="BD48:BJ50"/>
-    <mergeCell ref="V39:AB41"/>
-    <mergeCell ref="AT21:BG23"/>
-    <mergeCell ref="BD39:BJ41"/>
+    <mergeCell ref="BO1:BZ1"/>
+    <mergeCell ref="BO4:BZ4"/>
+    <mergeCell ref="BP43:BV43"/>
+    <mergeCell ref="Z1:BB2"/>
+    <mergeCell ref="BC4:BN4"/>
+    <mergeCell ref="N6:Y6"/>
+    <mergeCell ref="R21:AE23"/>
+    <mergeCell ref="AP42:AV44"/>
+    <mergeCell ref="O48:U50"/>
+    <mergeCell ref="Z5:BB6"/>
+    <mergeCell ref="AF24:AS26"/>
+    <mergeCell ref="BC5:BN5"/>
+    <mergeCell ref="N1:Y5"/>
+    <mergeCell ref="AC48:AO50"/>
+    <mergeCell ref="AT24:BG26"/>
+    <mergeCell ref="R24:AE26"/>
+    <mergeCell ref="BK36:BZ36"/>
+    <mergeCell ref="AW42:BC44"/>
+    <mergeCell ref="V45:AB47"/>
+    <mergeCell ref="BO2:BZ2"/>
+    <mergeCell ref="AP45:AV47"/>
+    <mergeCell ref="AW45:BC47"/>
+    <mergeCell ref="BO3:BZ3"/>
+    <mergeCell ref="BO5:BZ5"/>
+    <mergeCell ref="O42:U44"/>
+    <mergeCell ref="AF27:AS29"/>
+    <mergeCell ref="BC3:BN3"/>
+    <mergeCell ref="AT27:BG29"/>
+    <mergeCell ref="BD45:BJ47"/>
+    <mergeCell ref="AC45:AO47"/>
+    <mergeCell ref="V42:AB44"/>
     <mergeCell ref="A6:M6"/>
     <mergeCell ref="V48:AB50"/>
     <mergeCell ref="BC1:BN1"/>
@@ -4350,38 +4415,13 @@
     <mergeCell ref="AF21:AS23"/>
     <mergeCell ref="BC2:BN2"/>
     <mergeCell ref="AC39:AO41"/>
+    <mergeCell ref="Z3:BB4"/>
+    <mergeCell ref="BO6:BZ6"/>
+    <mergeCell ref="BD48:BJ50"/>
+    <mergeCell ref="V39:AB41"/>
+    <mergeCell ref="AT21:BG23"/>
+    <mergeCell ref="BD39:BJ41"/>
     <mergeCell ref="AP48:AV50"/>
-    <mergeCell ref="O42:U44"/>
-    <mergeCell ref="AF27:AS29"/>
-    <mergeCell ref="BC3:BN3"/>
-    <mergeCell ref="AT27:BG29"/>
-    <mergeCell ref="BD45:BJ47"/>
-    <mergeCell ref="AC45:AO47"/>
-    <mergeCell ref="O48:U50"/>
-    <mergeCell ref="Z5:BB6"/>
-    <mergeCell ref="AF24:AS26"/>
-    <mergeCell ref="BC5:BN5"/>
-    <mergeCell ref="N1:Y5"/>
-    <mergeCell ref="AC48:AO50"/>
-    <mergeCell ref="AT24:BG26"/>
-    <mergeCell ref="R24:AE26"/>
-    <mergeCell ref="BK36:BZ36"/>
-    <mergeCell ref="AW42:BC44"/>
-    <mergeCell ref="V45:AB47"/>
-    <mergeCell ref="BO2:BZ2"/>
-    <mergeCell ref="AP45:AV47"/>
-    <mergeCell ref="AW45:BC47"/>
-    <mergeCell ref="BO3:BZ3"/>
-    <mergeCell ref="BO5:BZ5"/>
-    <mergeCell ref="V42:AB44"/>
-    <mergeCell ref="Z1:BB2"/>
-    <mergeCell ref="BC4:BN4"/>
-    <mergeCell ref="N6:Y6"/>
-    <mergeCell ref="R21:AE23"/>
-    <mergeCell ref="AP42:AV44"/>
-    <mergeCell ref="BO1:BZ1"/>
-    <mergeCell ref="BO4:BZ4"/>
-    <mergeCell ref="BP43:BV43"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.39370078740157483" bottom="0.39370078740157483" header="3.937007874015748E-2" footer="3.937007874015748E-2"/>
@@ -4395,7 +4435,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O62"/>
+  <dimension ref="A1:O60"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="80.05" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="15" width="35" customWidth="1"/>
@@ -4410,151 +4450,151 @@
     <col min="62" max="62" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="84" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.9">
-      <c r="A1" s="78"/>
-      <c r="B1" s="79"/>
-      <c r="C1" s="78" t="str">
+    <row r="1" spans="1:15" s="22" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="A1" s="29"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="29" t="str">
         <f>PORTADA!Z1</f>
         <v>DISEÑO DE INGENIERÍA</v>
       </c>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="80"/>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
-      <c r="J1" s="80"/>
-      <c r="K1" s="80"/>
-      <c r="L1" s="81"/>
-      <c r="M1" s="82" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="N1" s="83" t="str">
+      <c r="N1" s="32" t="str">
         <f>PORTADA!BO1</f>
         <v>P2437-HV-DTS-003</v>
       </c>
-      <c r="O1" s="81"/>
-    </row>
-    <row r="2" spans="1:15" s="84" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.9">
-      <c r="A2" s="85"/>
-      <c r="B2" s="85"/>
-      <c r="C2" s="78" t="str">
+      <c r="O1" s="31"/>
+    </row>
+    <row r="2" spans="1:15" s="22" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="A2" s="41"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="29" t="str">
         <f>PORTADA!Z3</f>
         <v>SISTEMA HVAC LABORATORIO BRINSA</v>
       </c>
-      <c r="D2" s="86"/>
-      <c r="E2" s="86"/>
-      <c r="F2" s="86"/>
-      <c r="G2" s="86"/>
-      <c r="H2" s="86"/>
-      <c r="I2" s="86"/>
-      <c r="J2" s="86"/>
-      <c r="K2" s="86"/>
-      <c r="L2" s="87"/>
-      <c r="M2" s="82" t="s">
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="34"/>
+      <c r="M2" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="83" t="str">
+      <c r="N2" s="32" t="str">
         <f>PORTADA!BO2</f>
         <v>CERO (0)</v>
       </c>
-      <c r="O2" s="81"/>
-    </row>
-    <row r="3" spans="1:15" s="84" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.9">
-      <c r="A3" s="85"/>
-      <c r="B3" s="85"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="89"/>
-      <c r="E3" s="89"/>
-      <c r="F3" s="89"/>
-      <c r="G3" s="89"/>
-      <c r="H3" s="89"/>
-      <c r="I3" s="89"/>
-      <c r="J3" s="89"/>
-      <c r="K3" s="89"/>
-      <c r="L3" s="90"/>
-      <c r="M3" s="82" t="s">
+      <c r="O2" s="31"/>
+    </row>
+    <row r="3" spans="1:15" s="22" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="A3" s="41"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="40"/>
+      <c r="M3" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="83" t="str">
+      <c r="N3" s="32" t="str">
         <f>PORTADA!BO3</f>
         <v>JULIO 23 DEL 2026</v>
       </c>
-      <c r="O3" s="81"/>
-    </row>
-    <row r="4" spans="1:15" s="84" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.9">
-      <c r="A4" s="85"/>
-      <c r="B4" s="85"/>
-      <c r="C4" s="78" t="str">
+      <c r="O3" s="31"/>
+    </row>
+    <row r="4" spans="1:15" s="22" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="A4" s="41"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="29" t="str">
         <f>PORTADA!Z5</f>
         <v>HOJA DE DATOS Y ESPECIFICACIONES TÉCNICAS DE LAS REJILLAS DE EXFILTRACIÓN</v>
       </c>
-      <c r="D4" s="86"/>
-      <c r="E4" s="86"/>
-      <c r="F4" s="86"/>
-      <c r="G4" s="86"/>
-      <c r="H4" s="86"/>
-      <c r="I4" s="86"/>
-      <c r="J4" s="86"/>
-      <c r="K4" s="86"/>
-      <c r="L4" s="87"/>
-      <c r="M4" s="82" t="s">
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="33"/>
+      <c r="J4" s="33"/>
+      <c r="K4" s="33"/>
+      <c r="L4" s="34"/>
+      <c r="M4" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="N4" s="83" t="str">
+      <c r="N4" s="32" t="str">
         <f>PORTADA!BO4</f>
         <v>J.ARBOLEDA</v>
       </c>
-      <c r="O4" s="81"/>
-    </row>
-    <row r="5" spans="1:15" s="84" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.9">
-      <c r="A5" s="91"/>
-      <c r="B5" s="91"/>
-      <c r="C5" s="92"/>
-      <c r="D5" s="93"/>
-      <c r="E5" s="93"/>
-      <c r="F5" s="93"/>
-      <c r="G5" s="93"/>
-      <c r="H5" s="93"/>
-      <c r="I5" s="93"/>
-      <c r="J5" s="93"/>
-      <c r="K5" s="93"/>
-      <c r="L5" s="94"/>
-      <c r="M5" s="82" t="s">
+      <c r="O4" s="31"/>
+    </row>
+    <row r="5" spans="1:15" s="22" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="A5" s="42"/>
+      <c r="B5" s="42"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="36"/>
+      <c r="I5" s="36"/>
+      <c r="J5" s="36"/>
+      <c r="K5" s="36"/>
+      <c r="L5" s="37"/>
+      <c r="M5" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="N5" s="83" t="str">
+      <c r="N5" s="32" t="str">
         <f>PORTADA!BO5</f>
         <v>F.NAVIA</v>
       </c>
-      <c r="O5" s="81"/>
-    </row>
-    <row r="6" spans="1:15" s="84" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.9">
-      <c r="A6" s="82" t="s">
+      <c r="O5" s="31"/>
+    </row>
+    <row r="6" spans="1:15" s="22" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="A6" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="95" t="str">
+      <c r="B6" s="20" t="str">
         <f>PORTADA!N6</f>
         <v>P2437</v>
       </c>
-      <c r="C6" s="88"/>
-      <c r="D6" s="89"/>
-      <c r="E6" s="89"/>
-      <c r="F6" s="89"/>
-      <c r="G6" s="89"/>
-      <c r="H6" s="89"/>
-      <c r="I6" s="89"/>
-      <c r="J6" s="89"/>
-      <c r="K6" s="89"/>
-      <c r="L6" s="90"/>
-      <c r="M6" s="82" t="s">
+      <c r="C6" s="38"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="39"/>
+      <c r="K6" s="39"/>
+      <c r="L6" s="40"/>
+      <c r="M6" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="N6" s="83" t="str">
+      <c r="N6" s="32" t="str">
         <f>PORTADA!BO6</f>
         <v>H.ROSERO</v>
       </c>
-      <c r="O6" s="81"/>
+      <c r="O6" s="31"/>
     </row>
     <row r="7" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="15">
@@ -4604,988 +4644,1021 @@
       </c>
     </row>
     <row r="8" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="68" t="s">
+      <c r="A8" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="69"/>
-      <c r="C8" s="69"/>
-      <c r="D8" s="69"/>
-      <c r="E8" s="69"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="69"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="69"/>
-      <c r="J8" s="69"/>
-      <c r="K8" s="69"/>
-      <c r="L8" s="69"/>
-      <c r="M8" s="69"/>
-      <c r="N8" s="69"/>
-      <c r="O8" s="69"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="25"/>
+      <c r="I8" s="25"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="25"/>
+      <c r="L8" s="25"/>
+      <c r="M8" s="25"/>
+      <c r="N8" s="25"/>
+      <c r="O8" s="25"/>
     </row>
     <row r="9" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="67" t="s">
+      <c r="A9" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="67"/>
-      <c r="C9" s="67"/>
-      <c r="D9" s="67"/>
-      <c r="E9" s="67"/>
-      <c r="F9" s="67"/>
-      <c r="G9" s="67"/>
-      <c r="H9" s="67"/>
-      <c r="I9" s="67" t="s">
+      <c r="B9" s="28"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="J9" s="67"/>
-      <c r="K9" s="67"/>
-      <c r="L9" s="67"/>
-      <c r="M9" s="67"/>
-      <c r="N9" s="67"/>
-      <c r="O9" s="67"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="28"/>
+      <c r="L9" s="28"/>
+      <c r="M9" s="28"/>
+      <c r="N9" s="28"/>
+      <c r="O9" s="28"/>
     </row>
     <row r="10" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="65" t="s">
+      <c r="A10" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="66"/>
-      <c r="C10" s="66"/>
-      <c r="D10" s="66"/>
-      <c r="E10" s="66"/>
-      <c r="F10" s="66"/>
-      <c r="G10" s="66"/>
-      <c r="H10" s="66"/>
-      <c r="I10" s="65" t="s">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="J10" s="66"/>
-      <c r="K10" s="66"/>
-      <c r="L10" s="66"/>
-      <c r="M10" s="66"/>
-      <c r="N10" s="66"/>
-      <c r="O10" s="66"/>
+      <c r="J10" s="27"/>
+      <c r="K10" s="27"/>
+      <c r="L10" s="27"/>
+      <c r="M10" s="27"/>
+      <c r="N10" s="27"/>
+      <c r="O10" s="27"/>
     </row>
     <row r="11" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="65" t="s">
+      <c r="A11" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="66"/>
-      <c r="C11" s="66"/>
-      <c r="D11" s="66"/>
-      <c r="E11" s="66"/>
-      <c r="F11" s="66"/>
-      <c r="G11" s="66"/>
-      <c r="H11" s="66"/>
-      <c r="I11" s="65" t="s">
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="J11" s="66"/>
-      <c r="K11" s="66"/>
-      <c r="L11" s="66"/>
-      <c r="M11" s="66"/>
-      <c r="N11" s="66"/>
-      <c r="O11" s="66"/>
+      <c r="J11" s="27"/>
+      <c r="K11" s="27"/>
+      <c r="L11" s="27"/>
+      <c r="M11" s="27"/>
+      <c r="N11" s="27"/>
+      <c r="O11" s="27"/>
     </row>
     <row r="12" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="65" t="s">
+      <c r="A12" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="66"/>
-      <c r="C12" s="66"/>
-      <c r="D12" s="66"/>
-      <c r="E12" s="66"/>
-      <c r="F12" s="66"/>
-      <c r="G12" s="66"/>
-      <c r="H12" s="66"/>
-      <c r="I12" s="65" t="s">
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="J12" s="66"/>
-      <c r="K12" s="66"/>
-      <c r="L12" s="66"/>
-      <c r="M12" s="66"/>
-      <c r="N12" s="66"/>
-      <c r="O12" s="66"/>
+      <c r="J12" s="27"/>
+      <c r="K12" s="27"/>
+      <c r="L12" s="27"/>
+      <c r="M12" s="27"/>
+      <c r="N12" s="27"/>
+      <c r="O12" s="27"/>
     </row>
     <row r="13" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="65" t="s">
+      <c r="A13" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="66"/>
-      <c r="C13" s="66"/>
-      <c r="D13" s="66"/>
-      <c r="E13" s="66"/>
-      <c r="F13" s="66"/>
-      <c r="G13" s="66"/>
-      <c r="H13" s="66"/>
-      <c r="I13" s="65" t="s">
+      <c r="B13" s="27"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="J13" s="66"/>
-      <c r="K13" s="66"/>
-      <c r="L13" s="66"/>
-      <c r="M13" s="66"/>
-      <c r="N13" s="66"/>
-      <c r="O13" s="66"/>
+      <c r="J13" s="27"/>
+      <c r="K13" s="27"/>
+      <c r="L13" s="27"/>
+      <c r="M13" s="27"/>
+      <c r="N13" s="27"/>
+      <c r="O13" s="27"/>
     </row>
     <row r="14" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="65" t="s">
+      <c r="A14" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="66"/>
-      <c r="C14" s="66"/>
-      <c r="D14" s="66"/>
-      <c r="E14" s="66"/>
-      <c r="F14" s="66"/>
-      <c r="G14" s="66"/>
-      <c r="H14" s="66"/>
-      <c r="I14" s="65" t="s">
+      <c r="B14" s="27"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="27"/>
+      <c r="I14" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="J14" s="66"/>
-      <c r="K14" s="66"/>
-      <c r="L14" s="66"/>
-      <c r="M14" s="66"/>
-      <c r="N14" s="66"/>
-      <c r="O14" s="66"/>
+      <c r="J14" s="27"/>
+      <c r="K14" s="27"/>
+      <c r="L14" s="27"/>
+      <c r="M14" s="27"/>
+      <c r="N14" s="27"/>
+      <c r="O14" s="27"/>
     </row>
     <row r="15" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="16" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="68" t="s">
+      <c r="A16" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="69"/>
-      <c r="C16" s="69"/>
-      <c r="D16" s="69"/>
-      <c r="E16" s="69"/>
-      <c r="F16" s="69"/>
-      <c r="G16" s="69"/>
-      <c r="H16" s="69"/>
-      <c r="I16" s="69"/>
-      <c r="J16" s="69"/>
-      <c r="K16" s="69"/>
-      <c r="L16" s="69"/>
-      <c r="M16" s="69"/>
-      <c r="N16" s="69"/>
-      <c r="O16" s="69"/>
-    </row>
-    <row r="17" spans="1:15" ht="100.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="70" t="s">
+      <c r="B16" s="25"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="25"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="25"/>
+      <c r="K16" s="25"/>
+      <c r="L16" s="25"/>
+      <c r="M16" s="25"/>
+      <c r="N16" s="25"/>
+      <c r="O16" s="25"/>
+    </row>
+    <row r="17" spans="1:15" ht="101.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="70"/>
-      <c r="C17" s="70"/>
-      <c r="D17" s="70"/>
-      <c r="E17" s="70"/>
-      <c r="F17" s="70"/>
-      <c r="G17" s="70"/>
-      <c r="H17" s="70"/>
-      <c r="I17" s="70"/>
-      <c r="J17" s="70"/>
-      <c r="K17" s="70"/>
-      <c r="L17" s="70"/>
-      <c r="M17" s="70"/>
-      <c r="N17" s="70"/>
-      <c r="O17" s="70"/>
-    </row>
-    <row r="18" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="19" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="68" t="s">
+      <c r="B17" s="23"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="23"/>
+      <c r="H17" s="23"/>
+      <c r="I17" s="23"/>
+      <c r="J17" s="23"/>
+      <c r="K17" s="23"/>
+      <c r="L17" s="23"/>
+      <c r="M17" s="23"/>
+      <c r="N17" s="23"/>
+      <c r="O17" s="23"/>
+    </row>
+    <row r="18" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="B19" s="69"/>
-      <c r="C19" s="69"/>
-      <c r="D19" s="69"/>
-      <c r="E19" s="69"/>
-      <c r="F19" s="69"/>
-      <c r="G19" s="69"/>
-      <c r="H19" s="69"/>
-      <c r="I19" s="69"/>
-      <c r="J19" s="69"/>
-      <c r="K19" s="69"/>
-      <c r="L19" s="69"/>
-      <c r="M19" s="69"/>
-      <c r="N19" s="69"/>
-      <c r="O19" s="69"/>
+      <c r="B18" s="25"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="25"/>
+      <c r="K18" s="25"/>
+      <c r="L18" s="25"/>
+      <c r="M18" s="25"/>
+      <c r="N18" s="25"/>
+      <c r="O18" s="25"/>
+    </row>
+    <row r="19" spans="1:15" ht="64.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="17" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="20" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="71" t="s">
-        <v>48</v>
-      </c>
+      <c r="A20" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" s="28"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
+      <c r="I20" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="J20" s="28"/>
+      <c r="K20" s="28"/>
+      <c r="L20" s="28"/>
+      <c r="M20" s="28"/>
+      <c r="N20" s="28"/>
+      <c r="O20" s="28"/>
     </row>
     <row r="21" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="67" t="s">
-        <v>49</v>
-      </c>
-      <c r="B21" s="67"/>
-      <c r="C21" s="67"/>
-      <c r="D21" s="67"/>
-      <c r="E21" s="67"/>
-      <c r="F21" s="67"/>
-      <c r="G21" s="67"/>
-      <c r="H21" s="67"/>
-      <c r="I21" s="67" t="s">
-        <v>34</v>
-      </c>
-      <c r="J21" s="67"/>
-      <c r="K21" s="67"/>
-      <c r="L21" s="67"/>
-      <c r="M21" s="67"/>
-      <c r="N21" s="67"/>
-      <c r="O21" s="67"/>
+      <c r="A21" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" s="27"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="27"/>
+      <c r="F21" s="27"/>
+      <c r="G21" s="27"/>
+      <c r="H21" s="27"/>
+      <c r="I21" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="J21" s="27"/>
+      <c r="K21" s="27"/>
+      <c r="L21" s="27"/>
+      <c r="M21" s="27"/>
+      <c r="N21" s="27"/>
+      <c r="O21" s="27"/>
     </row>
     <row r="22" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="65" t="s">
-        <v>50</v>
-      </c>
-      <c r="B22" s="66"/>
-      <c r="C22" s="66"/>
-      <c r="D22" s="66"/>
-      <c r="E22" s="66"/>
-      <c r="F22" s="66"/>
-      <c r="G22" s="66"/>
-      <c r="H22" s="66"/>
-      <c r="I22" s="65" t="s">
-        <v>51</v>
-      </c>
-      <c r="J22" s="66"/>
-      <c r="K22" s="66"/>
-      <c r="L22" s="66"/>
-      <c r="M22" s="66"/>
-      <c r="N22" s="66"/>
-      <c r="O22" s="66"/>
+      <c r="A22" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" s="27"/>
+      <c r="C22" s="27"/>
+      <c r="D22" s="27"/>
+      <c r="E22" s="27"/>
+      <c r="F22" s="27"/>
+      <c r="G22" s="27"/>
+      <c r="H22" s="27"/>
+      <c r="I22" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="J22" s="27"/>
+      <c r="K22" s="27"/>
+      <c r="L22" s="27"/>
+      <c r="M22" s="27"/>
+      <c r="N22" s="27"/>
+      <c r="O22" s="27"/>
     </row>
     <row r="23" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="B23" s="66"/>
-      <c r="C23" s="66"/>
-      <c r="D23" s="66"/>
-      <c r="E23" s="66"/>
-      <c r="F23" s="66"/>
-      <c r="G23" s="66"/>
-      <c r="H23" s="66"/>
-      <c r="I23" s="65" t="s">
+      <c r="A23" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" s="27"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="27"/>
+      <c r="I23" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="J23" s="27"/>
+      <c r="K23" s="27"/>
+      <c r="L23" s="27"/>
+      <c r="M23" s="27"/>
+      <c r="N23" s="27"/>
+      <c r="O23" s="27"/>
+    </row>
+    <row r="24" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" s="27"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="27"/>
+      <c r="G24" s="27"/>
+      <c r="H24" s="27"/>
+      <c r="I24" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="J24" s="27"/>
+      <c r="K24" s="27"/>
+      <c r="L24" s="27"/>
+      <c r="M24" s="27"/>
+      <c r="N24" s="27"/>
+      <c r="O24" s="27"/>
+    </row>
+    <row r="25" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="B25" s="27"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="27"/>
+      <c r="E25" s="27"/>
+      <c r="F25" s="27"/>
+      <c r="G25" s="27"/>
+      <c r="H25" s="27"/>
+      <c r="I25" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="J25" s="27"/>
+      <c r="K25" s="27"/>
+      <c r="L25" s="27"/>
+      <c r="M25" s="27"/>
+      <c r="N25" s="27"/>
+      <c r="O25" s="27"/>
+    </row>
+    <row r="26" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26" s="27"/>
+      <c r="C26" s="27"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="27"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="27"/>
+      <c r="I26" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="J26" s="27"/>
+      <c r="K26" s="27"/>
+      <c r="L26" s="27"/>
+      <c r="M26" s="27"/>
+      <c r="N26" s="27"/>
+      <c r="O26" s="27"/>
+    </row>
+    <row r="27" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="B27" s="27"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="27"/>
+      <c r="F27" s="27"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="27"/>
+      <c r="I27" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="J27" s="27"/>
+      <c r="K27" s="27"/>
+      <c r="L27" s="27"/>
+      <c r="M27" s="27"/>
+      <c r="N27" s="27"/>
+      <c r="O27" s="27"/>
+    </row>
+    <row r="28" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="29" spans="1:15" ht="80.599999999999994" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="B29" s="23"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="23"/>
+      <c r="E29" s="23"/>
+      <c r="F29" s="23"/>
+      <c r="G29" s="23"/>
+      <c r="H29" s="23"/>
+      <c r="I29" s="23"/>
+      <c r="J29" s="23"/>
+      <c r="K29" s="23"/>
+      <c r="L29" s="23"/>
+      <c r="M29" s="23"/>
+      <c r="N29" s="23"/>
+      <c r="O29" s="23"/>
+    </row>
+    <row r="30" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="31" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="B31" s="25"/>
+      <c r="C31" s="25"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="25"/>
+      <c r="G31" s="25"/>
+      <c r="H31" s="25"/>
+      <c r="I31" s="25"/>
+      <c r="J31" s="25"/>
+      <c r="K31" s="25"/>
+      <c r="L31" s="25"/>
+      <c r="M31" s="25"/>
+      <c r="N31" s="25"/>
+      <c r="O31" s="25"/>
+    </row>
+    <row r="32" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="16" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="B33" s="28"/>
+      <c r="C33" s="28"/>
+      <c r="D33" s="28"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="28"/>
+      <c r="G33" s="28"/>
+      <c r="H33" s="28"/>
+      <c r="I33" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="J33" s="28"/>
+      <c r="K33" s="28"/>
+      <c r="L33" s="28"/>
+      <c r="M33" s="28"/>
+      <c r="N33" s="28"/>
+      <c r="O33" s="28"/>
+    </row>
+    <row r="34" spans="1:15" ht="64.849999999999994" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A34" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="B34" s="27"/>
+      <c r="C34" s="27"/>
+      <c r="D34" s="27"/>
+      <c r="E34" s="27"/>
+      <c r="F34" s="27"/>
+      <c r="G34" s="27"/>
+      <c r="H34" s="27"/>
+      <c r="I34" s="94" t="s">
+        <v>69</v>
+      </c>
+      <c r="J34" s="95"/>
+      <c r="K34" s="95"/>
+      <c r="L34" s="95"/>
+      <c r="M34" s="95"/>
+      <c r="N34" s="95"/>
+      <c r="O34" s="95"/>
+    </row>
+    <row r="35" spans="1:15" ht="64.849999999999994" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A35" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="B35" s="27"/>
+      <c r="C35" s="27"/>
+      <c r="D35" s="27"/>
+      <c r="E35" s="27"/>
+      <c r="F35" s="27"/>
+      <c r="G35" s="27"/>
+      <c r="H35" s="27"/>
+      <c r="I35" s="94" t="s">
+        <v>71</v>
+      </c>
+      <c r="J35" s="95"/>
+      <c r="K35" s="95"/>
+      <c r="L35" s="95"/>
+      <c r="M35" s="95"/>
+      <c r="N35" s="95"/>
+      <c r="O35" s="95"/>
+    </row>
+    <row r="36" spans="1:15" ht="64.849999999999994" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A36" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="B36" s="27"/>
+      <c r="C36" s="27"/>
+      <c r="D36" s="27"/>
+      <c r="E36" s="27"/>
+      <c r="F36" s="27"/>
+      <c r="G36" s="27"/>
+      <c r="H36" s="27"/>
+      <c r="I36" s="94" t="s">
+        <v>73</v>
+      </c>
+      <c r="J36" s="95"/>
+      <c r="K36" s="95"/>
+      <c r="L36" s="95"/>
+      <c r="M36" s="95"/>
+      <c r="N36" s="95"/>
+      <c r="O36" s="95"/>
+    </row>
+    <row r="37" spans="1:15" ht="64.849999999999994" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A37" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="B37" s="27"/>
+      <c r="C37" s="27"/>
+      <c r="D37" s="27"/>
+      <c r="E37" s="27"/>
+      <c r="F37" s="27"/>
+      <c r="G37" s="27"/>
+      <c r="H37" s="27"/>
+      <c r="I37" s="94" t="s">
+        <v>75</v>
+      </c>
+      <c r="J37" s="95"/>
+      <c r="K37" s="95"/>
+      <c r="L37" s="95"/>
+      <c r="M37" s="95"/>
+      <c r="N37" s="95"/>
+      <c r="O37" s="95"/>
+    </row>
+    <row r="38" spans="1:15" ht="64.849999999999994" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A38" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="B38" s="27"/>
+      <c r="C38" s="27"/>
+      <c r="D38" s="27"/>
+      <c r="E38" s="27"/>
+      <c r="F38" s="27"/>
+      <c r="G38" s="27"/>
+      <c r="H38" s="27"/>
+      <c r="I38" s="94" t="s">
+        <v>77</v>
+      </c>
+      <c r="J38" s="95"/>
+      <c r="K38" s="95"/>
+      <c r="L38" s="95"/>
+      <c r="M38" s="95"/>
+      <c r="N38" s="95"/>
+      <c r="O38" s="95"/>
+    </row>
+    <row r="39" spans="1:15" ht="64.849999999999994" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A39" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B39" s="27"/>
+      <c r="C39" s="27"/>
+      <c r="D39" s="27"/>
+      <c r="E39" s="27"/>
+      <c r="F39" s="27"/>
+      <c r="G39" s="27"/>
+      <c r="H39" s="27"/>
+      <c r="I39" s="94" t="s">
+        <v>79</v>
+      </c>
+      <c r="J39" s="95"/>
+      <c r="K39" s="95"/>
+      <c r="L39" s="95"/>
+      <c r="M39" s="95"/>
+      <c r="N39" s="95"/>
+      <c r="O39" s="95"/>
+    </row>
+    <row r="40" spans="1:15" ht="64.849999999999994" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A40" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="B40" s="27"/>
+      <c r="C40" s="27"/>
+      <c r="D40" s="27"/>
+      <c r="E40" s="27"/>
+      <c r="F40" s="27"/>
+      <c r="G40" s="27"/>
+      <c r="H40" s="27"/>
+      <c r="I40" s="94" t="s">
+        <v>81</v>
+      </c>
+      <c r="J40" s="95"/>
+      <c r="K40" s="95"/>
+      <c r="L40" s="95"/>
+      <c r="M40" s="95"/>
+      <c r="N40" s="95"/>
+      <c r="O40" s="95"/>
+    </row>
+    <row r="41" spans="1:15" ht="64.849999999999994" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A41" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="B41" s="27"/>
+      <c r="C41" s="27"/>
+      <c r="D41" s="27"/>
+      <c r="E41" s="27"/>
+      <c r="F41" s="27"/>
+      <c r="G41" s="27"/>
+      <c r="H41" s="27"/>
+      <c r="I41" s="94" t="s">
+        <v>83</v>
+      </c>
+      <c r="J41" s="95"/>
+      <c r="K41" s="95"/>
+      <c r="L41" s="95"/>
+      <c r="M41" s="95"/>
+      <c r="N41" s="95"/>
+      <c r="O41" s="95"/>
+    </row>
+    <row r="42" spans="1:15" ht="64.849999999999994" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A42" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B42" s="27"/>
+      <c r="C42" s="27"/>
+      <c r="D42" s="27"/>
+      <c r="E42" s="27"/>
+      <c r="F42" s="27"/>
+      <c r="G42" s="27"/>
+      <c r="H42" s="27"/>
+      <c r="I42" s="94" t="s">
+        <v>85</v>
+      </c>
+      <c r="J42" s="95"/>
+      <c r="K42" s="95"/>
+      <c r="L42" s="95"/>
+      <c r="M42" s="95"/>
+      <c r="N42" s="95"/>
+      <c r="O42" s="95"/>
+    </row>
+    <row r="43" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="44" spans="1:15" ht="58.85" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="B44" s="23"/>
+      <c r="C44" s="23"/>
+      <c r="D44" s="23"/>
+      <c r="E44" s="23"/>
+      <c r="F44" s="23"/>
+      <c r="G44" s="23"/>
+      <c r="H44" s="23"/>
+      <c r="I44" s="23"/>
+      <c r="J44" s="23"/>
+      <c r="K44" s="23"/>
+      <c r="L44" s="23"/>
+      <c r="M44" s="23"/>
+      <c r="N44" s="23"/>
+      <c r="O44" s="23"/>
+    </row>
+    <row r="45" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="46" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A46" s="97" t="s">
         <v>125</v>
       </c>
-      <c r="J23" s="66"/>
-      <c r="K23" s="66"/>
-      <c r="L23" s="66"/>
-      <c r="M23" s="66"/>
-      <c r="N23" s="66"/>
-      <c r="O23" s="66"/>
-    </row>
-    <row r="24" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="65" t="s">
-        <v>53</v>
-      </c>
-      <c r="B24" s="66"/>
-      <c r="C24" s="66"/>
-      <c r="D24" s="66"/>
-      <c r="E24" s="66"/>
-      <c r="F24" s="66"/>
-      <c r="G24" s="66"/>
-      <c r="H24" s="66"/>
-      <c r="I24" s="65" t="s">
-        <v>54</v>
-      </c>
-      <c r="J24" s="66"/>
-      <c r="K24" s="66"/>
-      <c r="L24" s="66"/>
-      <c r="M24" s="66"/>
-      <c r="N24" s="66"/>
-      <c r="O24" s="66"/>
-    </row>
-    <row r="25" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="65" t="s">
-        <v>55</v>
-      </c>
-      <c r="B25" s="66"/>
-      <c r="C25" s="66"/>
-      <c r="D25" s="66"/>
-      <c r="E25" s="66"/>
-      <c r="F25" s="66"/>
-      <c r="G25" s="66"/>
-      <c r="H25" s="66"/>
-      <c r="I25" s="65" t="s">
-        <v>56</v>
-      </c>
-      <c r="J25" s="66"/>
-      <c r="K25" s="66"/>
-      <c r="L25" s="66"/>
-      <c r="M25" s="66"/>
-      <c r="N25" s="66"/>
-      <c r="O25" s="66"/>
-    </row>
-    <row r="26" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="65" t="s">
-        <v>57</v>
-      </c>
-      <c r="B26" s="66"/>
-      <c r="C26" s="66"/>
-      <c r="D26" s="66"/>
-      <c r="E26" s="66"/>
-      <c r="F26" s="66"/>
-      <c r="G26" s="66"/>
-      <c r="H26" s="66"/>
-      <c r="I26" s="65" t="s">
-        <v>58</v>
-      </c>
-      <c r="J26" s="66"/>
-      <c r="K26" s="66"/>
-      <c r="L26" s="66"/>
-      <c r="M26" s="66"/>
-      <c r="N26" s="66"/>
-      <c r="O26" s="66"/>
-    </row>
-    <row r="27" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="65" t="s">
-        <v>59</v>
-      </c>
-      <c r="B27" s="66"/>
-      <c r="C27" s="66"/>
-      <c r="D27" s="66"/>
-      <c r="E27" s="66"/>
-      <c r="F27" s="66"/>
-      <c r="G27" s="66"/>
-      <c r="H27" s="66"/>
-      <c r="I27" s="65" t="s">
-        <v>60</v>
-      </c>
-      <c r="J27" s="66"/>
-      <c r="K27" s="66"/>
-      <c r="L27" s="66"/>
-      <c r="M27" s="66"/>
-      <c r="N27" s="66"/>
-      <c r="O27" s="66"/>
-    </row>
-    <row r="28" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="65" t="s">
-        <v>61</v>
-      </c>
-      <c r="B28" s="66"/>
-      <c r="C28" s="66"/>
-      <c r="D28" s="66"/>
-      <c r="E28" s="66"/>
-      <c r="F28" s="66"/>
-      <c r="G28" s="66"/>
-      <c r="H28" s="66"/>
-      <c r="I28" s="65" t="s">
-        <v>62</v>
-      </c>
-      <c r="J28" s="66"/>
-      <c r="K28" s="66"/>
-      <c r="L28" s="66"/>
-      <c r="M28" s="66"/>
-      <c r="N28" s="66"/>
-      <c r="O28" s="66"/>
-    </row>
-    <row r="29" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="30" spans="1:15" ht="80.599999999999994" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="70" t="s">
-        <v>63</v>
-      </c>
-      <c r="B30" s="70"/>
-      <c r="C30" s="70"/>
-      <c r="D30" s="70"/>
-      <c r="E30" s="70"/>
-      <c r="F30" s="70"/>
-      <c r="G30" s="70"/>
-      <c r="H30" s="70"/>
-      <c r="I30" s="70"/>
-      <c r="J30" s="70"/>
-      <c r="K30" s="70"/>
-      <c r="L30" s="70"/>
-      <c r="M30" s="70"/>
-      <c r="N30" s="70"/>
-      <c r="O30" s="70"/>
-    </row>
-    <row r="31" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="32" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="68" t="s">
-        <v>64</v>
-      </c>
-      <c r="B32" s="69"/>
-      <c r="C32" s="69"/>
-      <c r="D32" s="69"/>
-      <c r="E32" s="69"/>
-      <c r="F32" s="69"/>
-      <c r="G32" s="69"/>
-      <c r="H32" s="69"/>
-      <c r="I32" s="69"/>
-      <c r="J32" s="69"/>
-      <c r="K32" s="69"/>
-      <c r="L32" s="69"/>
-      <c r="M32" s="69"/>
-      <c r="N32" s="69"/>
-      <c r="O32" s="69"/>
-    </row>
-    <row r="33" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="16" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="67" t="s">
-        <v>66</v>
-      </c>
-      <c r="B34" s="67"/>
-      <c r="C34" s="67"/>
-      <c r="D34" s="67"/>
-      <c r="E34" s="67"/>
-      <c r="F34" s="67"/>
-      <c r="G34" s="67"/>
-      <c r="H34" s="67"/>
-      <c r="I34" s="67" t="s">
-        <v>67</v>
-      </c>
-      <c r="J34" s="67"/>
-      <c r="K34" s="67"/>
-      <c r="L34" s="67"/>
-      <c r="M34" s="67"/>
-      <c r="N34" s="67"/>
-      <c r="O34" s="67"/>
-    </row>
-    <row r="35" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="A35" s="65" t="s">
-        <v>68</v>
-      </c>
-      <c r="B35" s="66"/>
-      <c r="C35" s="66"/>
-      <c r="D35" s="66"/>
-      <c r="E35" s="66"/>
-      <c r="F35" s="66"/>
-      <c r="G35" s="66"/>
-      <c r="H35" s="66"/>
-      <c r="I35" s="74" t="s">
-        <v>69</v>
-      </c>
-      <c r="J35" s="75"/>
-      <c r="K35" s="75"/>
-      <c r="L35" s="75"/>
-      <c r="M35" s="75"/>
-      <c r="N35" s="75"/>
-      <c r="O35" s="75"/>
-    </row>
-    <row r="36" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="A36" s="65" t="s">
-        <v>70</v>
-      </c>
-      <c r="B36" s="66"/>
-      <c r="C36" s="66"/>
-      <c r="D36" s="66"/>
-      <c r="E36" s="66"/>
-      <c r="F36" s="66"/>
-      <c r="G36" s="66"/>
-      <c r="H36" s="66"/>
-      <c r="I36" s="74" t="s">
-        <v>71</v>
-      </c>
-      <c r="J36" s="75"/>
-      <c r="K36" s="75"/>
-      <c r="L36" s="75"/>
-      <c r="M36" s="75"/>
-      <c r="N36" s="75"/>
-      <c r="O36" s="75"/>
-    </row>
-    <row r="37" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="A37" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="B37" s="66"/>
-      <c r="C37" s="66"/>
-      <c r="D37" s="66"/>
-      <c r="E37" s="66"/>
-      <c r="F37" s="66"/>
-      <c r="G37" s="66"/>
-      <c r="H37" s="66"/>
-      <c r="I37" s="74" t="s">
-        <v>73</v>
-      </c>
-      <c r="J37" s="75"/>
-      <c r="K37" s="75"/>
-      <c r="L37" s="75"/>
-      <c r="M37" s="75"/>
-      <c r="N37" s="75"/>
-      <c r="O37" s="75"/>
-    </row>
-    <row r="38" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="A38" s="65" t="s">
-        <v>74</v>
-      </c>
-      <c r="B38" s="66"/>
-      <c r="C38" s="66"/>
-      <c r="D38" s="66"/>
-      <c r="E38" s="66"/>
-      <c r="F38" s="66"/>
-      <c r="G38" s="66"/>
-      <c r="H38" s="66"/>
-      <c r="I38" s="74" t="s">
-        <v>75</v>
-      </c>
-      <c r="J38" s="75"/>
-      <c r="K38" s="75"/>
-      <c r="L38" s="75"/>
-      <c r="M38" s="75"/>
-      <c r="N38" s="75"/>
-      <c r="O38" s="75"/>
-    </row>
-    <row r="39" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="A39" s="65" t="s">
-        <v>76</v>
-      </c>
-      <c r="B39" s="66"/>
-      <c r="C39" s="66"/>
-      <c r="D39" s="66"/>
-      <c r="E39" s="66"/>
-      <c r="F39" s="66"/>
-      <c r="G39" s="66"/>
-      <c r="H39" s="66"/>
-      <c r="I39" s="74" t="s">
-        <v>77</v>
-      </c>
-      <c r="J39" s="75"/>
-      <c r="K39" s="75"/>
-      <c r="L39" s="75"/>
-      <c r="M39" s="75"/>
-      <c r="N39" s="75"/>
-      <c r="O39" s="75"/>
-    </row>
-    <row r="40" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="A40" s="65" t="s">
-        <v>78</v>
-      </c>
-      <c r="B40" s="66"/>
-      <c r="C40" s="66"/>
-      <c r="D40" s="66"/>
-      <c r="E40" s="66"/>
-      <c r="F40" s="66"/>
-      <c r="G40" s="66"/>
-      <c r="H40" s="66"/>
-      <c r="I40" s="74" t="s">
-        <v>79</v>
-      </c>
-      <c r="J40" s="75"/>
-      <c r="K40" s="75"/>
-      <c r="L40" s="75"/>
-      <c r="M40" s="75"/>
-      <c r="N40" s="75"/>
-      <c r="O40" s="75"/>
-    </row>
-    <row r="41" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="A41" s="65" t="s">
-        <v>80</v>
-      </c>
-      <c r="B41" s="66"/>
-      <c r="C41" s="66"/>
-      <c r="D41" s="66"/>
-      <c r="E41" s="66"/>
-      <c r="F41" s="66"/>
-      <c r="G41" s="66"/>
-      <c r="H41" s="66"/>
-      <c r="I41" s="74" t="s">
-        <v>81</v>
-      </c>
-      <c r="J41" s="75"/>
-      <c r="K41" s="75"/>
-      <c r="L41" s="75"/>
-      <c r="M41" s="75"/>
-      <c r="N41" s="75"/>
-      <c r="O41" s="75"/>
-    </row>
-    <row r="42" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="A42" s="65" t="s">
-        <v>82</v>
-      </c>
-      <c r="B42" s="66"/>
-      <c r="C42" s="66"/>
-      <c r="D42" s="66"/>
-      <c r="E42" s="66"/>
-      <c r="F42" s="66"/>
-      <c r="G42" s="66"/>
-      <c r="H42" s="66"/>
-      <c r="I42" s="74" t="s">
-        <v>83</v>
-      </c>
-      <c r="J42" s="75"/>
-      <c r="K42" s="75"/>
-      <c r="L42" s="75"/>
-      <c r="M42" s="75"/>
-      <c r="N42" s="75"/>
-      <c r="O42" s="75"/>
-    </row>
-    <row r="43" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="A43" s="65" t="s">
-        <v>84</v>
-      </c>
-      <c r="B43" s="66"/>
-      <c r="C43" s="66"/>
-      <c r="D43" s="66"/>
-      <c r="E43" s="66"/>
-      <c r="F43" s="66"/>
-      <c r="G43" s="66"/>
-      <c r="H43" s="66"/>
-      <c r="I43" s="74" t="s">
-        <v>85</v>
-      </c>
-      <c r="J43" s="75"/>
-      <c r="K43" s="75"/>
-      <c r="L43" s="75"/>
-      <c r="M43" s="75"/>
-      <c r="N43" s="75"/>
-      <c r="O43" s="75"/>
-    </row>
-    <row r="44" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="45" spans="1:15" ht="58.85" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="70" t="s">
-        <v>86</v>
-      </c>
-      <c r="B45" s="70"/>
-      <c r="C45" s="70"/>
-      <c r="D45" s="70"/>
-      <c r="E45" s="70"/>
-      <c r="F45" s="70"/>
-      <c r="G45" s="70"/>
-      <c r="H45" s="70"/>
-      <c r="I45" s="70"/>
-      <c r="J45" s="70"/>
-      <c r="K45" s="70"/>
-      <c r="L45" s="70"/>
-      <c r="M45" s="70"/>
-      <c r="N45" s="70"/>
-      <c r="O45" s="70"/>
-    </row>
-    <row r="46" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.4"/>
+      <c r="B46" s="25"/>
+      <c r="C46" s="25"/>
+      <c r="D46" s="25"/>
+      <c r="E46" s="25"/>
+      <c r="F46" s="25"/>
+      <c r="G46" s="25"/>
+      <c r="H46" s="25"/>
+      <c r="I46" s="25"/>
+      <c r="J46" s="25"/>
+      <c r="K46" s="25"/>
+      <c r="L46" s="25"/>
+      <c r="M46" s="25"/>
+      <c r="N46" s="25"/>
+      <c r="O46" s="25"/>
+    </row>
     <row r="47" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="68" t="s">
+      <c r="A47" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="B47" s="69"/>
-      <c r="C47" s="69"/>
-      <c r="D47" s="69"/>
-      <c r="E47" s="69"/>
-      <c r="F47" s="69"/>
-      <c r="G47" s="69"/>
-      <c r="H47" s="69"/>
-      <c r="I47" s="69"/>
-      <c r="J47" s="69"/>
-      <c r="K47" s="69"/>
-      <c r="L47" s="69"/>
-      <c r="M47" s="69"/>
-      <c r="N47" s="69"/>
-      <c r="O47" s="69"/>
-    </row>
-    <row r="48" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="16" t="s">
+    </row>
+    <row r="48" spans="1:15" ht="87" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="28" t="s">
         <v>88</v>
       </c>
+      <c r="B48" s="28"/>
+      <c r="C48" s="28"/>
+      <c r="D48" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="E48" s="28"/>
+      <c r="F48" s="28"/>
+      <c r="G48" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="H48" s="28"/>
+      <c r="I48" s="28"/>
+      <c r="J48" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="K48" s="28"/>
+      <c r="L48" s="28"/>
+      <c r="M48" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="N48" s="28"/>
+      <c r="O48" s="28"/>
     </row>
     <row r="49" spans="1:15" ht="87" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="67" t="s">
-        <v>89</v>
-      </c>
-      <c r="B49" s="67"/>
-      <c r="C49" s="67"/>
-      <c r="D49" s="67" t="s">
-        <v>90</v>
-      </c>
-      <c r="E49" s="67"/>
-      <c r="F49" s="67"/>
-      <c r="G49" s="67" t="s">
-        <v>91</v>
-      </c>
-      <c r="H49" s="67"/>
-      <c r="I49" s="67"/>
-      <c r="J49" s="67" t="s">
-        <v>92</v>
-      </c>
-      <c r="K49" s="67"/>
-      <c r="L49" s="67"/>
-      <c r="M49" s="67" t="s">
+      <c r="A49" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="N49" s="67"/>
-      <c r="O49" s="67"/>
+      <c r="B49" s="27"/>
+      <c r="C49" s="27"/>
+      <c r="D49" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="E49" s="27"/>
+      <c r="F49" s="27"/>
+      <c r="G49" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="H49" s="27"/>
+      <c r="I49" s="27"/>
+      <c r="J49" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="K49" s="27"/>
+      <c r="L49" s="27"/>
+      <c r="M49" s="43" t="s">
+        <v>97</v>
+      </c>
+      <c r="N49" s="44"/>
+      <c r="O49" s="44"/>
     </row>
     <row r="50" spans="1:15" ht="87" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="65" t="s">
-        <v>94</v>
-      </c>
-      <c r="B50" s="66"/>
-      <c r="C50" s="66"/>
-      <c r="D50" s="65" t="s">
-        <v>95</v>
-      </c>
-      <c r="E50" s="66"/>
-      <c r="F50" s="66"/>
-      <c r="G50" s="65" t="s">
-        <v>96</v>
-      </c>
-      <c r="H50" s="66"/>
-      <c r="I50" s="66"/>
-      <c r="J50" s="65" t="s">
-        <v>97</v>
-      </c>
-      <c r="K50" s="66"/>
-      <c r="L50" s="66"/>
-      <c r="M50" s="76" t="s">
+      <c r="A50" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="N50" s="77"/>
-      <c r="O50" s="77"/>
+      <c r="B50" s="27"/>
+      <c r="C50" s="27"/>
+      <c r="D50" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="E50" s="27"/>
+      <c r="F50" s="27"/>
+      <c r="G50" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="H50" s="27"/>
+      <c r="I50" s="27"/>
+      <c r="J50" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="K50" s="27"/>
+      <c r="L50" s="27"/>
+      <c r="M50" s="43" t="s">
+        <v>102</v>
+      </c>
+      <c r="N50" s="44"/>
+      <c r="O50" s="44"/>
     </row>
     <row r="51" spans="1:15" ht="87" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="65" t="s">
-        <v>99</v>
-      </c>
-      <c r="B51" s="66"/>
-      <c r="C51" s="66"/>
-      <c r="D51" s="65" t="s">
-        <v>100</v>
-      </c>
-      <c r="E51" s="66"/>
-      <c r="F51" s="66"/>
-      <c r="G51" s="65" t="s">
-        <v>101</v>
-      </c>
-      <c r="H51" s="66"/>
-      <c r="I51" s="66"/>
-      <c r="J51" s="65" t="s">
-        <v>102</v>
-      </c>
-      <c r="K51" s="66"/>
-      <c r="L51" s="66"/>
-      <c r="M51" s="76" t="s">
+      <c r="A51" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="N51" s="77"/>
-      <c r="O51" s="77"/>
+      <c r="B51" s="27"/>
+      <c r="C51" s="27"/>
+      <c r="D51" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="E51" s="27"/>
+      <c r="F51" s="27"/>
+      <c r="G51" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="H51" s="27"/>
+      <c r="I51" s="27"/>
+      <c r="J51" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="K51" s="27"/>
+      <c r="L51" s="27"/>
+      <c r="M51" s="43" t="s">
+        <v>107</v>
+      </c>
+      <c r="N51" s="44"/>
+      <c r="O51" s="44"/>
     </row>
     <row r="52" spans="1:15" ht="87" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="65" t="s">
-        <v>104</v>
-      </c>
-      <c r="B52" s="66"/>
-      <c r="C52" s="66"/>
-      <c r="D52" s="65" t="s">
-        <v>105</v>
-      </c>
-      <c r="E52" s="66"/>
-      <c r="F52" s="66"/>
-      <c r="G52" s="65" t="s">
-        <v>106</v>
-      </c>
-      <c r="H52" s="66"/>
-      <c r="I52" s="66"/>
-      <c r="J52" s="65" t="s">
-        <v>107</v>
-      </c>
-      <c r="K52" s="66"/>
-      <c r="L52" s="66"/>
-      <c r="M52" s="76" t="s">
+      <c r="A52" s="26" t="s">
         <v>108</v>
       </c>
-      <c r="N52" s="77"/>
-      <c r="O52" s="77"/>
+      <c r="B52" s="27"/>
+      <c r="C52" s="27"/>
+      <c r="D52" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="E52" s="27"/>
+      <c r="F52" s="27"/>
+      <c r="G52" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="H52" s="27"/>
+      <c r="I52" s="27"/>
+      <c r="J52" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="K52" s="27"/>
+      <c r="L52" s="27"/>
+      <c r="M52" s="43" t="s">
+        <v>112</v>
+      </c>
+      <c r="N52" s="44"/>
+      <c r="O52" s="44"/>
     </row>
     <row r="53" spans="1:15" ht="87" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="65" t="s">
-        <v>109</v>
-      </c>
-      <c r="B53" s="66"/>
-      <c r="C53" s="66"/>
-      <c r="D53" s="65" t="s">
-        <v>110</v>
-      </c>
-      <c r="E53" s="66"/>
-      <c r="F53" s="66"/>
-      <c r="G53" s="65" t="s">
-        <v>111</v>
-      </c>
-      <c r="H53" s="66"/>
-      <c r="I53" s="66"/>
-      <c r="J53" s="65" t="s">
-        <v>112</v>
-      </c>
-      <c r="K53" s="66"/>
-      <c r="L53" s="66"/>
-      <c r="M53" s="76" t="s">
+      <c r="A53" s="26" t="s">
         <v>113</v>
       </c>
-      <c r="N53" s="77"/>
-      <c r="O53" s="77"/>
-    </row>
-    <row r="54" spans="1:15" ht="87" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="65" t="s">
+      <c r="B53" s="27"/>
+      <c r="C53" s="27"/>
+      <c r="D53" s="26" t="s">
         <v>114</v>
       </c>
-      <c r="B54" s="66"/>
-      <c r="C54" s="66"/>
-      <c r="D54" s="65" t="s">
+      <c r="E53" s="27"/>
+      <c r="F53" s="27"/>
+      <c r="G53" s="26" t="s">
         <v>115</v>
       </c>
-      <c r="E54" s="66"/>
-      <c r="F54" s="66"/>
-      <c r="G54" s="65" t="s">
+      <c r="H53" s="27"/>
+      <c r="I53" s="27"/>
+      <c r="J53" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="H54" s="66"/>
-      <c r="I54" s="66"/>
-      <c r="J54" s="65" t="s">
+      <c r="K53" s="27"/>
+      <c r="L53" s="27"/>
+      <c r="M53" s="43" t="s">
         <v>117</v>
       </c>
-      <c r="K54" s="66"/>
-      <c r="L54" s="66"/>
-      <c r="M54" s="76" t="s">
+      <c r="N53" s="44"/>
+      <c r="O53" s="44"/>
+    </row>
+    <row r="54" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="55" spans="1:15" ht="133.30000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A55" s="24" t="s">
         <v>118</v>
       </c>
-      <c r="N54" s="77"/>
-      <c r="O54" s="77"/>
-    </row>
-    <row r="55" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="56" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="68" t="s">
+      <c r="B55" s="25"/>
+      <c r="C55" s="25"/>
+      <c r="D55" s="25"/>
+      <c r="E55" s="25"/>
+      <c r="F55" s="25"/>
+      <c r="G55" s="25"/>
+      <c r="H55" s="25"/>
+      <c r="I55" s="25"/>
+      <c r="J55" s="25"/>
+      <c r="K55" s="25"/>
+      <c r="L55" s="25"/>
+      <c r="M55" s="25"/>
+      <c r="N55" s="25"/>
+      <c r="O55" s="25"/>
+    </row>
+    <row r="56" spans="1:15" ht="133.30000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A56" s="96" t="s">
+        <v>124</v>
+      </c>
+      <c r="B56" s="23"/>
+      <c r="C56" s="23"/>
+      <c r="D56" s="23"/>
+      <c r="E56" s="23"/>
+      <c r="F56" s="23"/>
+      <c r="G56" s="23"/>
+      <c r="H56" s="23"/>
+      <c r="I56" s="23"/>
+      <c r="J56" s="23"/>
+      <c r="K56" s="23"/>
+      <c r="L56" s="23"/>
+      <c r="M56" s="23"/>
+      <c r="N56" s="23"/>
+      <c r="O56" s="23"/>
+    </row>
+    <row r="57" spans="1:15" ht="133.30000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A57" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="B56" s="69"/>
-      <c r="C56" s="69"/>
-      <c r="D56" s="69"/>
-      <c r="E56" s="69"/>
-      <c r="F56" s="69"/>
-      <c r="G56" s="69"/>
-      <c r="H56" s="69"/>
-      <c r="I56" s="69"/>
-      <c r="J56" s="69"/>
-      <c r="K56" s="69"/>
-      <c r="L56" s="69"/>
-      <c r="M56" s="69"/>
-      <c r="N56" s="69"/>
-      <c r="O56" s="69"/>
-    </row>
-    <row r="57" spans="1:15" ht="103.3" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="70" t="s">
+      <c r="B57" s="19"/>
+      <c r="C57" s="19"/>
+      <c r="D57" s="19"/>
+      <c r="E57" s="19"/>
+      <c r="F57" s="19"/>
+      <c r="G57" s="19"/>
+      <c r="H57" s="19"/>
+      <c r="I57" s="19"/>
+      <c r="J57" s="19"/>
+      <c r="K57" s="19"/>
+      <c r="L57" s="19"/>
+      <c r="M57" s="19"/>
+      <c r="N57" s="19"/>
+      <c r="O57" s="19"/>
+    </row>
+    <row r="58" spans="1:15" ht="133.30000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A58" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="B57" s="70"/>
-      <c r="C57" s="70"/>
-      <c r="D57" s="70"/>
-      <c r="E57" s="70"/>
-      <c r="F57" s="70"/>
-      <c r="G57" s="70"/>
-      <c r="H57" s="70"/>
-      <c r="I57" s="70"/>
-      <c r="J57" s="70"/>
-      <c r="K57" s="70"/>
-      <c r="L57" s="70"/>
-      <c r="M57" s="70"/>
-      <c r="N57" s="70"/>
-      <c r="O57" s="70"/>
-    </row>
-    <row r="58" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="72" t="s">
+      <c r="B58" s="19"/>
+      <c r="C58" s="19"/>
+      <c r="D58" s="19"/>
+      <c r="E58" s="19"/>
+      <c r="F58" s="19"/>
+      <c r="G58" s="19"/>
+      <c r="H58" s="19"/>
+      <c r="I58" s="19"/>
+      <c r="J58" s="19"/>
+      <c r="K58" s="19"/>
+      <c r="L58" s="19"/>
+      <c r="M58" s="19"/>
+      <c r="N58" s="19"/>
+      <c r="O58" s="19"/>
+    </row>
+    <row r="59" spans="1:15" ht="133.30000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A59" s="24" t="s">
         <v>121</v>
       </c>
-      <c r="B58" s="73"/>
-      <c r="C58" s="73"/>
-      <c r="D58" s="73"/>
-      <c r="E58" s="73"/>
-      <c r="F58" s="73"/>
-      <c r="G58" s="73"/>
-      <c r="H58" s="73"/>
-      <c r="I58" s="73"/>
-      <c r="J58" s="73"/>
-      <c r="K58" s="73"/>
-      <c r="L58" s="73"/>
-      <c r="M58" s="73"/>
-      <c r="N58" s="73"/>
-      <c r="O58" s="73"/>
-    </row>
-    <row r="59" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="72" t="s">
+      <c r="B59" s="25"/>
+      <c r="C59" s="25"/>
+      <c r="D59" s="25"/>
+      <c r="E59" s="25"/>
+      <c r="F59" s="25"/>
+      <c r="G59" s="25"/>
+      <c r="H59" s="25"/>
+      <c r="I59" s="25"/>
+      <c r="J59" s="25"/>
+      <c r="K59" s="25"/>
+      <c r="L59" s="25"/>
+      <c r="M59" s="25"/>
+      <c r="N59" s="25"/>
+      <c r="O59" s="25"/>
+    </row>
+    <row r="60" spans="1:15" ht="133.30000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A60" s="23" t="s">
         <v>122</v>
       </c>
-      <c r="B59" s="73"/>
-      <c r="C59" s="73"/>
-      <c r="D59" s="73"/>
-      <c r="E59" s="73"/>
-      <c r="F59" s="73"/>
-      <c r="G59" s="73"/>
-      <c r="H59" s="73"/>
-      <c r="I59" s="73"/>
-      <c r="J59" s="73"/>
-      <c r="K59" s="73"/>
-      <c r="L59" s="73"/>
-      <c r="M59" s="73"/>
-      <c r="N59" s="73"/>
-      <c r="O59" s="73"/>
-    </row>
-    <row r="60" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="61" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="68" t="s">
-        <v>123</v>
-      </c>
-      <c r="B61" s="69"/>
-      <c r="C61" s="69"/>
-      <c r="D61" s="69"/>
-      <c r="E61" s="69"/>
-      <c r="F61" s="69"/>
-      <c r="G61" s="69"/>
-      <c r="H61" s="69"/>
-      <c r="I61" s="69"/>
-      <c r="J61" s="69"/>
-      <c r="K61" s="69"/>
-      <c r="L61" s="69"/>
-      <c r="M61" s="69"/>
-      <c r="N61" s="69"/>
-      <c r="O61" s="69"/>
-    </row>
-    <row r="62" spans="1:15" ht="110.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="70" t="s">
-        <v>124</v>
-      </c>
-      <c r="B62" s="70"/>
-      <c r="C62" s="70"/>
-      <c r="D62" s="70"/>
-      <c r="E62" s="70"/>
-      <c r="F62" s="70"/>
-      <c r="G62" s="70"/>
-      <c r="H62" s="70"/>
-      <c r="I62" s="70"/>
-      <c r="J62" s="70"/>
-      <c r="K62" s="70"/>
-      <c r="L62" s="70"/>
-      <c r="M62" s="70"/>
-      <c r="N62" s="70"/>
-      <c r="O62" s="70"/>
+      <c r="B60" s="23"/>
+      <c r="C60" s="23"/>
+      <c r="D60" s="23"/>
+      <c r="E60" s="23"/>
+      <c r="F60" s="23"/>
+      <c r="G60" s="23"/>
+      <c r="H60" s="23"/>
+      <c r="I60" s="23"/>
+      <c r="J60" s="23"/>
+      <c r="K60" s="23"/>
+      <c r="L60" s="23"/>
+      <c r="M60" s="23"/>
+      <c r="N60" s="23"/>
+      <c r="O60" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="101">
-    <mergeCell ref="A57:O57"/>
-    <mergeCell ref="A62:O62"/>
-    <mergeCell ref="A56:O56"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="J48:L48"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="C2:L3"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="G48:I48"/>
+    <mergeCell ref="J50:L50"/>
+    <mergeCell ref="M51:O51"/>
+    <mergeCell ref="G50:I50"/>
     <mergeCell ref="I39:O39"/>
-    <mergeCell ref="I14:O14"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="I22:O22"/>
+    <mergeCell ref="B1:B5"/>
+    <mergeCell ref="J52:L52"/>
+    <mergeCell ref="M49:O49"/>
     <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="I37:O37"/>
+    <mergeCell ref="M52:O52"/>
+    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="I36:O36"/>
+    <mergeCell ref="M53:O53"/>
     <mergeCell ref="A36:H36"/>
-    <mergeCell ref="J50:L50"/>
-    <mergeCell ref="I25:O25"/>
-    <mergeCell ref="M49:O49"/>
+    <mergeCell ref="M50:O50"/>
+    <mergeCell ref="I41:O41"/>
+    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="I42:O42"/>
+    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="A1:A5"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="G53:I53"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="G49:I49"/>
+    <mergeCell ref="A59:O59"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="I10:O10"/>
+    <mergeCell ref="G52:I52"/>
+    <mergeCell ref="A18:O18"/>
+    <mergeCell ref="D52:F52"/>
+    <mergeCell ref="A40:H40"/>
+    <mergeCell ref="A46:O46"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="I26:O26"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="I35:O35"/>
+    <mergeCell ref="A14:H14"/>
     <mergeCell ref="A22:H22"/>
-    <mergeCell ref="I24:O24"/>
-    <mergeCell ref="A42:H42"/>
-    <mergeCell ref="D51:F51"/>
-    <mergeCell ref="I41:O41"/>
-    <mergeCell ref="A17:O17"/>
-    <mergeCell ref="A30:O30"/>
-    <mergeCell ref="A45:O45"/>
+    <mergeCell ref="I33:O33"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="I9:O9"/>
+    <mergeCell ref="J53:L53"/>
     <mergeCell ref="A8:O8"/>
     <mergeCell ref="C1:L1"/>
-    <mergeCell ref="I21:O21"/>
-    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="I20:O20"/>
+    <mergeCell ref="A33:H33"/>
     <mergeCell ref="A9:H9"/>
     <mergeCell ref="I11:O11"/>
     <mergeCell ref="I13:O13"/>
-    <mergeCell ref="I28:O28"/>
+    <mergeCell ref="I27:O27"/>
     <mergeCell ref="A10:H10"/>
     <mergeCell ref="I12:O12"/>
     <mergeCell ref="N1:O1"/>
@@ -5593,74 +5666,39 @@
     <mergeCell ref="A13:H13"/>
     <mergeCell ref="C4:L6"/>
     <mergeCell ref="N6:O6"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="I21:O21"/>
+    <mergeCell ref="A31:O31"/>
+    <mergeCell ref="A16:O16"/>
+    <mergeCell ref="I25:O25"/>
+    <mergeCell ref="A24:H24"/>
     <mergeCell ref="A27:H27"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="J52:L52"/>
-    <mergeCell ref="I22:O22"/>
-    <mergeCell ref="G52:I52"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A32:O32"/>
-    <mergeCell ref="A40:H40"/>
-    <mergeCell ref="A16:O16"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="A56:O56"/>
+    <mergeCell ref="A60:O60"/>
+    <mergeCell ref="A55:O55"/>
+    <mergeCell ref="I38:O38"/>
+    <mergeCell ref="I14:O14"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A35:H35"/>
+    <mergeCell ref="J49:L49"/>
+    <mergeCell ref="I24:O24"/>
+    <mergeCell ref="M48:O48"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="I23:O23"/>
+    <mergeCell ref="A41:H41"/>
     <mergeCell ref="D50:F50"/>
-    <mergeCell ref="I26:O26"/>
-    <mergeCell ref="A25:H25"/>
-    <mergeCell ref="I35:O35"/>
+    <mergeCell ref="I40:O40"/>
+    <mergeCell ref="A17:O17"/>
+    <mergeCell ref="A29:O29"/>
+    <mergeCell ref="A44:O44"/>
+    <mergeCell ref="J51:L51"/>
+    <mergeCell ref="G51:I51"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A39:H39"/>
     <mergeCell ref="D49:F49"/>
-    <mergeCell ref="A1:A5"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="G54:I54"/>
-    <mergeCell ref="A26:H26"/>
-    <mergeCell ref="G50:I50"/>
-    <mergeCell ref="A61:O61"/>
-    <mergeCell ref="D54:F54"/>
-    <mergeCell ref="I10:O10"/>
-    <mergeCell ref="G53:I53"/>
-    <mergeCell ref="A19:O19"/>
-    <mergeCell ref="D53:F53"/>
-    <mergeCell ref="A41:H41"/>
-    <mergeCell ref="A47:O47"/>
-    <mergeCell ref="A21:H21"/>
-    <mergeCell ref="I27:O27"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="I36:O36"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A23:H23"/>
     <mergeCell ref="I34:O34"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="I9:O9"/>
-    <mergeCell ref="J54:L54"/>
-    <mergeCell ref="J53:L53"/>
-    <mergeCell ref="M50:O50"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A38:H38"/>
-    <mergeCell ref="I38:O38"/>
-    <mergeCell ref="M53:O53"/>
-    <mergeCell ref="A35:H35"/>
-    <mergeCell ref="I37:O37"/>
-    <mergeCell ref="M54:O54"/>
-    <mergeCell ref="A28:H28"/>
-    <mergeCell ref="A37:H37"/>
-    <mergeCell ref="M51:O51"/>
-    <mergeCell ref="I42:O42"/>
-    <mergeCell ref="A43:H43"/>
-    <mergeCell ref="A39:H39"/>
-    <mergeCell ref="I43:O43"/>
-    <mergeCell ref="D52:F52"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="A24:H24"/>
-    <mergeCell ref="J49:L49"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="C2:L3"/>
-    <mergeCell ref="A51:C51"/>
-    <mergeCell ref="G49:I49"/>
-    <mergeCell ref="J51:L51"/>
-    <mergeCell ref="M52:O52"/>
-    <mergeCell ref="G51:I51"/>
-    <mergeCell ref="I40:O40"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="I23:O23"/>
-    <mergeCell ref="B1:B5"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.11811023622047245" bottom="0.11811023622047245" header="0" footer="0"/>
